--- a/templates/invoice_template_v2.xlsx
+++ b/templates/invoice_template_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Проекты\Агент Авто Континент\01_БОТ_АКТУАЛЬНЫЙ\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F54B77-5205-4222-A6BC-5BEF5FBB4471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13229A1E-40D4-46EF-89C2-7DFBF17ED111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -250,7 +250,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -287,43 +287,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -448,20 +411,100 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -473,7 +516,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -485,104 +528,121 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -946,440 +1006,440 @@
     </row>
     <row r="2" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
-      <c r="S2" s="13"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="26" t="s">
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="V2" s="27"/>
-      <c r="W2" s="27"/>
-      <c r="X2" s="28"/>
-      <c r="Y2" s="43" t="s">
+      <c r="V2" s="49"/>
+      <c r="W2" s="49"/>
+      <c r="X2" s="52"/>
+      <c r="Y2" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="Z2" s="13"/>
-      <c r="AA2" s="13"/>
-      <c r="AB2" s="13"/>
-      <c r="AC2" s="13"/>
-      <c r="AD2" s="13"/>
-      <c r="AE2" s="13"/>
-      <c r="AF2" s="13"/>
-      <c r="AG2" s="13"/>
-      <c r="AH2" s="13"/>
-      <c r="AI2" s="13"/>
-      <c r="AJ2" s="13"/>
-      <c r="AK2" s="13"/>
-      <c r="AL2" s="30"/>
+      <c r="Z2" s="28"/>
+      <c r="AA2" s="28"/>
+      <c r="AB2" s="28"/>
+      <c r="AC2" s="28"/>
+      <c r="AD2" s="28"/>
+      <c r="AE2" s="28"/>
+      <c r="AF2" s="28"/>
+      <c r="AG2" s="28"/>
+      <c r="AH2" s="28"/>
+      <c r="AI2" s="28"/>
+      <c r="AJ2" s="28"/>
+      <c r="AK2" s="28"/>
+      <c r="AL2" s="29"/>
     </row>
     <row r="3" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
-      <c r="N3" s="16"/>
-      <c r="O3" s="16"/>
-      <c r="P3" s="16"/>
-      <c r="Q3" s="16"/>
-      <c r="R3" s="16"/>
-      <c r="S3" s="16"/>
-      <c r="T3" s="35"/>
-      <c r="U3" s="29" t="s">
+      <c r="B3" s="30"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="17"/>
+      <c r="T3" s="45"/>
+      <c r="U3" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="V3" s="13"/>
-      <c r="W3" s="13"/>
-      <c r="X3" s="30"/>
-      <c r="Y3" s="37" t="s">
+      <c r="V3" s="45"/>
+      <c r="W3" s="45"/>
+      <c r="X3" s="54"/>
+      <c r="Y3" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="Z3" s="16"/>
-      <c r="AA3" s="16"/>
-      <c r="AB3" s="16"/>
-      <c r="AC3" s="16"/>
-      <c r="AD3" s="16"/>
-      <c r="AE3" s="16"/>
-      <c r="AF3" s="16"/>
-      <c r="AG3" s="16"/>
-      <c r="AH3" s="16"/>
-      <c r="AI3" s="16"/>
-      <c r="AJ3" s="16"/>
-      <c r="AK3" s="16"/>
-      <c r="AL3" s="35"/>
+      <c r="Z3" s="17"/>
+      <c r="AA3" s="17"/>
+      <c r="AB3" s="17"/>
+      <c r="AC3" s="17"/>
+      <c r="AD3" s="17"/>
+      <c r="AE3" s="17"/>
+      <c r="AF3" s="17"/>
+      <c r="AG3" s="17"/>
+      <c r="AH3" s="17"/>
+      <c r="AI3" s="17"/>
+      <c r="AJ3" s="17"/>
+      <c r="AK3" s="17"/>
+      <c r="AL3" s="31"/>
     </row>
     <row r="4" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
-      <c r="O4" s="32"/>
-      <c r="P4" s="32"/>
-      <c r="Q4" s="32"/>
-      <c r="R4" s="32"/>
-      <c r="S4" s="32"/>
-      <c r="T4" s="33"/>
-      <c r="U4" s="31"/>
-      <c r="V4" s="32"/>
-      <c r="W4" s="32"/>
-      <c r="X4" s="33"/>
-      <c r="Y4" s="31"/>
-      <c r="Z4" s="32"/>
-      <c r="AA4" s="32"/>
-      <c r="AB4" s="32"/>
-      <c r="AC4" s="32"/>
-      <c r="AD4" s="32"/>
-      <c r="AE4" s="32"/>
-      <c r="AF4" s="32"/>
-      <c r="AG4" s="32"/>
-      <c r="AH4" s="32"/>
-      <c r="AI4" s="32"/>
-      <c r="AJ4" s="32"/>
-      <c r="AK4" s="32"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="13"/>
+      <c r="T4" s="13"/>
+      <c r="U4" s="55"/>
+      <c r="V4" s="45"/>
+      <c r="W4" s="45"/>
+      <c r="X4" s="54"/>
+      <c r="Y4" s="13"/>
+      <c r="Z4" s="13"/>
+      <c r="AA4" s="13"/>
+      <c r="AB4" s="13"/>
+      <c r="AC4" s="13"/>
+      <c r="AD4" s="13"/>
+      <c r="AE4" s="13"/>
+      <c r="AF4" s="13"/>
+      <c r="AG4" s="13"/>
+      <c r="AH4" s="13"/>
+      <c r="AI4" s="13"/>
+      <c r="AJ4" s="13"/>
+      <c r="AK4" s="13"/>
       <c r="AL4" s="33"/>
     </row>
     <row r="5" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="13"/>
-      <c r="T5" s="30"/>
-      <c r="U5" s="26" t="s">
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="28"/>
+      <c r="T5" s="28"/>
+      <c r="U5" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="V5" s="27"/>
-      <c r="W5" s="27"/>
-      <c r="X5" s="28"/>
-      <c r="Y5" s="36" t="s">
+      <c r="V5" s="49"/>
+      <c r="W5" s="49"/>
+      <c r="X5" s="52"/>
+      <c r="Y5" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="Z5" s="13"/>
-      <c r="AA5" s="13"/>
-      <c r="AB5" s="13"/>
-      <c r="AC5" s="13"/>
-      <c r="AD5" s="13"/>
-      <c r="AE5" s="13"/>
-      <c r="AF5" s="13"/>
-      <c r="AG5" s="13"/>
-      <c r="AH5" s="13"/>
-      <c r="AI5" s="13"/>
-      <c r="AJ5" s="13"/>
-      <c r="AK5" s="13"/>
-      <c r="AL5" s="30"/>
+      <c r="Z5" s="28"/>
+      <c r="AA5" s="28"/>
+      <c r="AB5" s="28"/>
+      <c r="AC5" s="28"/>
+      <c r="AD5" s="28"/>
+      <c r="AE5" s="28"/>
+      <c r="AF5" s="28"/>
+      <c r="AG5" s="28"/>
+      <c r="AH5" s="28"/>
+      <c r="AI5" s="28"/>
+      <c r="AJ5" s="28"/>
+      <c r="AK5" s="28"/>
+      <c r="AL5" s="29"/>
     </row>
     <row r="6" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
-      <c r="S6" s="16"/>
-      <c r="T6" s="35"/>
-      <c r="U6" s="29" t="s">
+      <c r="B6" s="30"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="45"/>
+      <c r="U6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="13"/>
-      <c r="W6" s="13"/>
-      <c r="X6" s="30"/>
-      <c r="Y6" s="37" t="s">
+      <c r="V6" s="45"/>
+      <c r="W6" s="45"/>
+      <c r="X6" s="54"/>
+      <c r="Y6" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="Z6" s="16"/>
-      <c r="AA6" s="16"/>
-      <c r="AB6" s="16"/>
-      <c r="AC6" s="16"/>
-      <c r="AD6" s="16"/>
-      <c r="AE6" s="16"/>
-      <c r="AF6" s="16"/>
-      <c r="AG6" s="16"/>
-      <c r="AH6" s="16"/>
-      <c r="AI6" s="16"/>
-      <c r="AJ6" s="16"/>
-      <c r="AK6" s="16"/>
-      <c r="AL6" s="35"/>
+      <c r="Z6" s="17"/>
+      <c r="AA6" s="17"/>
+      <c r="AB6" s="17"/>
+      <c r="AC6" s="17"/>
+      <c r="AD6" s="17"/>
+      <c r="AE6" s="17"/>
+      <c r="AF6" s="17"/>
+      <c r="AG6" s="17"/>
+      <c r="AH6" s="17"/>
+      <c r="AI6" s="17"/>
+      <c r="AJ6" s="17"/>
+      <c r="AK6" s="17"/>
+      <c r="AL6" s="31"/>
     </row>
     <row r="7" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="32"/>
-      <c r="K7" s="32"/>
-      <c r="L7" s="32"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="32"/>
-      <c r="O7" s="32"/>
-      <c r="P7" s="32"/>
-      <c r="Q7" s="32"/>
-      <c r="R7" s="32"/>
-      <c r="S7" s="32"/>
-      <c r="T7" s="33"/>
-      <c r="U7" s="31"/>
-      <c r="V7" s="32"/>
-      <c r="W7" s="32"/>
-      <c r="X7" s="33"/>
-      <c r="Y7" s="31"/>
-      <c r="Z7" s="32"/>
-      <c r="AA7" s="32"/>
-      <c r="AB7" s="32"/>
-      <c r="AC7" s="32"/>
-      <c r="AD7" s="32"/>
-      <c r="AE7" s="32"/>
-      <c r="AF7" s="32"/>
-      <c r="AG7" s="32"/>
-      <c r="AH7" s="32"/>
-      <c r="AI7" s="32"/>
-      <c r="AJ7" s="32"/>
-      <c r="AK7" s="32"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="45"/>
+      <c r="L7" s="45"/>
+      <c r="M7" s="45"/>
+      <c r="N7" s="45"/>
+      <c r="O7" s="45"/>
+      <c r="P7" s="45"/>
+      <c r="Q7" s="45"/>
+      <c r="R7" s="45"/>
+      <c r="S7" s="45"/>
+      <c r="T7" s="45"/>
+      <c r="U7" s="63"/>
+      <c r="V7" s="58"/>
+      <c r="W7" s="58"/>
+      <c r="X7" s="59"/>
+      <c r="Y7" s="13"/>
+      <c r="Z7" s="13"/>
+      <c r="AA7" s="13"/>
+      <c r="AB7" s="13"/>
+      <c r="AC7" s="13"/>
+      <c r="AD7" s="13"/>
+      <c r="AE7" s="13"/>
+      <c r="AF7" s="13"/>
+      <c r="AG7" s="13"/>
+      <c r="AH7" s="13"/>
+      <c r="AI7" s="13"/>
+      <c r="AJ7" s="13"/>
+      <c r="AK7" s="13"/>
       <c r="AL7" s="33"/>
     </row>
     <row r="8" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="41" t="s">
+      <c r="C8" s="49"/>
+      <c r="D8" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="40" t="s">
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="L8" s="13"/>
-      <c r="M8" s="42"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="13"/>
-      <c r="S8" s="13"/>
-      <c r="T8" s="30"/>
-      <c r="U8" s="29" t="s">
+      <c r="L8" s="49"/>
+      <c r="M8" s="51"/>
+      <c r="N8" s="49"/>
+      <c r="O8" s="49"/>
+      <c r="P8" s="49"/>
+      <c r="Q8" s="49"/>
+      <c r="R8" s="49"/>
+      <c r="S8" s="49"/>
+      <c r="T8" s="52"/>
+      <c r="U8" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="V8" s="13"/>
-      <c r="W8" s="13"/>
-      <c r="X8" s="30"/>
+      <c r="V8" s="45"/>
+      <c r="W8" s="45"/>
+      <c r="X8" s="31"/>
       <c r="Y8" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="Z8" s="13"/>
-      <c r="AA8" s="13"/>
-      <c r="AB8" s="13"/>
-      <c r="AC8" s="13"/>
-      <c r="AD8" s="13"/>
-      <c r="AE8" s="13"/>
-      <c r="AF8" s="13"/>
-      <c r="AG8" s="13"/>
-      <c r="AH8" s="13"/>
-      <c r="AI8" s="13"/>
-      <c r="AJ8" s="13"/>
-      <c r="AK8" s="13"/>
-      <c r="AL8" s="30"/>
+      <c r="Z8" s="28"/>
+      <c r="AA8" s="28"/>
+      <c r="AB8" s="28"/>
+      <c r="AC8" s="28"/>
+      <c r="AD8" s="28"/>
+      <c r="AE8" s="28"/>
+      <c r="AF8" s="28"/>
+      <c r="AG8" s="28"/>
+      <c r="AH8" s="28"/>
+      <c r="AI8" s="28"/>
+      <c r="AJ8" s="28"/>
+      <c r="AK8" s="28"/>
+      <c r="AL8" s="29"/>
     </row>
     <row r="9" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
-      <c r="S9" s="13"/>
-      <c r="T9" s="13"/>
-      <c r="U9" s="34"/>
-      <c r="V9" s="16"/>
-      <c r="W9" s="16"/>
-      <c r="X9" s="35"/>
-      <c r="Y9" s="34"/>
-      <c r="Z9" s="16"/>
-      <c r="AA9" s="16"/>
-      <c r="AB9" s="16"/>
-      <c r="AC9" s="16"/>
-      <c r="AD9" s="16"/>
-      <c r="AE9" s="16"/>
-      <c r="AF9" s="16"/>
-      <c r="AG9" s="16"/>
-      <c r="AH9" s="16"/>
-      <c r="AI9" s="16"/>
-      <c r="AJ9" s="16"/>
-      <c r="AK9" s="16"/>
-      <c r="AL9" s="35"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="45"/>
+      <c r="J9" s="45"/>
+      <c r="K9" s="45"/>
+      <c r="L9" s="45"/>
+      <c r="M9" s="45"/>
+      <c r="N9" s="45"/>
+      <c r="O9" s="45"/>
+      <c r="P9" s="45"/>
+      <c r="Q9" s="45"/>
+      <c r="R9" s="45"/>
+      <c r="S9" s="45"/>
+      <c r="T9" s="54"/>
+      <c r="U9" s="45"/>
+      <c r="V9" s="17"/>
+      <c r="W9" s="17"/>
+      <c r="X9" s="31"/>
+      <c r="Y9" s="30"/>
+      <c r="Z9" s="17"/>
+      <c r="AA9" s="17"/>
+      <c r="AB9" s="17"/>
+      <c r="AC9" s="17"/>
+      <c r="AD9" s="17"/>
+      <c r="AE9" s="17"/>
+      <c r="AF9" s="17"/>
+      <c r="AG9" s="17"/>
+      <c r="AH9" s="17"/>
+      <c r="AI9" s="17"/>
+      <c r="AJ9" s="17"/>
+      <c r="AK9" s="17"/>
+      <c r="AL9" s="31"/>
     </row>
     <row r="10" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
-      <c r="B10" s="34"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
-      <c r="S10" s="16"/>
-      <c r="T10" s="16"/>
-      <c r="U10" s="34"/>
-      <c r="V10" s="16"/>
-      <c r="W10" s="16"/>
-      <c r="X10" s="35"/>
-      <c r="Y10" s="34"/>
-      <c r="Z10" s="16"/>
-      <c r="AA10" s="16"/>
-      <c r="AB10" s="16"/>
-      <c r="AC10" s="16"/>
-      <c r="AD10" s="16"/>
-      <c r="AE10" s="16"/>
-      <c r="AF10" s="16"/>
-      <c r="AG10" s="16"/>
-      <c r="AH10" s="16"/>
-      <c r="AI10" s="16"/>
-      <c r="AJ10" s="16"/>
-      <c r="AK10" s="16"/>
-      <c r="AL10" s="35"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46"/>
+      <c r="J10" s="46"/>
+      <c r="K10" s="46"/>
+      <c r="L10" s="46"/>
+      <c r="M10" s="46"/>
+      <c r="N10" s="46"/>
+      <c r="O10" s="46"/>
+      <c r="P10" s="46"/>
+      <c r="Q10" s="46"/>
+      <c r="R10" s="46"/>
+      <c r="S10" s="46"/>
+      <c r="T10" s="56"/>
+      <c r="U10" s="45"/>
+      <c r="V10" s="17"/>
+      <c r="W10" s="17"/>
+      <c r="X10" s="31"/>
+      <c r="Y10" s="30"/>
+      <c r="Z10" s="17"/>
+      <c r="AA10" s="17"/>
+      <c r="AB10" s="17"/>
+      <c r="AC10" s="17"/>
+      <c r="AD10" s="17"/>
+      <c r="AE10" s="17"/>
+      <c r="AF10" s="17"/>
+      <c r="AG10" s="17"/>
+      <c r="AH10" s="17"/>
+      <c r="AI10" s="17"/>
+      <c r="AJ10" s="17"/>
+      <c r="AK10" s="17"/>
+      <c r="AL10" s="31"/>
     </row>
     <row r="11" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="44" t="s">
+      <c r="B11" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-      <c r="K11" s="32"/>
-      <c r="L11" s="32"/>
-      <c r="M11" s="32"/>
-      <c r="N11" s="32"/>
-      <c r="O11" s="32"/>
-      <c r="P11" s="32"/>
-      <c r="Q11" s="32"/>
-      <c r="R11" s="32"/>
-      <c r="S11" s="32"/>
-      <c r="T11" s="32"/>
-      <c r="U11" s="31"/>
-      <c r="V11" s="32"/>
-      <c r="W11" s="32"/>
+      <c r="C11" s="58"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="58"/>
+      <c r="I11" s="58"/>
+      <c r="J11" s="58"/>
+      <c r="K11" s="58"/>
+      <c r="L11" s="58"/>
+      <c r="M11" s="58"/>
+      <c r="N11" s="58"/>
+      <c r="O11" s="58"/>
+      <c r="P11" s="58"/>
+      <c r="Q11" s="58"/>
+      <c r="R11" s="58"/>
+      <c r="S11" s="58"/>
+      <c r="T11" s="59"/>
+      <c r="U11" s="13"/>
+      <c r="V11" s="13"/>
+      <c r="W11" s="13"/>
       <c r="X11" s="33"/>
-      <c r="Y11" s="31"/>
-      <c r="Z11" s="32"/>
-      <c r="AA11" s="32"/>
-      <c r="AB11" s="32"/>
-      <c r="AC11" s="32"/>
-      <c r="AD11" s="32"/>
-      <c r="AE11" s="32"/>
-      <c r="AF11" s="32"/>
-      <c r="AG11" s="32"/>
-      <c r="AH11" s="32"/>
-      <c r="AI11" s="32"/>
-      <c r="AJ11" s="32"/>
-      <c r="AK11" s="32"/>
+      <c r="Y11" s="32"/>
+      <c r="Z11" s="13"/>
+      <c r="AA11" s="13"/>
+      <c r="AB11" s="13"/>
+      <c r="AC11" s="13"/>
+      <c r="AD11" s="13"/>
+      <c r="AE11" s="13"/>
+      <c r="AF11" s="13"/>
+      <c r="AG11" s="13"/>
+      <c r="AH11" s="13"/>
+      <c r="AI11" s="13"/>
+      <c r="AJ11" s="13"/>
+      <c r="AK11" s="13"/>
       <c r="AL11" s="33"/>
     </row>
     <row r="12" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1424,125 +1484,125 @@
     </row>
     <row r="13" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="46"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="46"/>
-      <c r="J13" s="46"/>
-      <c r="K13" s="46"/>
-      <c r="L13" s="46"/>
-      <c r="M13" s="46"/>
-      <c r="N13" s="46"/>
-      <c r="O13" s="46"/>
-      <c r="P13" s="46"/>
-      <c r="Q13" s="46"/>
-      <c r="R13" s="46"/>
-      <c r="S13" s="46"/>
-      <c r="T13" s="46"/>
-      <c r="U13" s="46"/>
-      <c r="V13" s="46"/>
-      <c r="W13" s="46"/>
-      <c r="X13" s="46"/>
-      <c r="Y13" s="46"/>
-      <c r="Z13" s="46"/>
-      <c r="AA13" s="46"/>
-      <c r="AB13" s="46"/>
-      <c r="AC13" s="46"/>
-      <c r="AD13" s="46"/>
-      <c r="AE13" s="46"/>
-      <c r="AF13" s="46"/>
-      <c r="AG13" s="46"/>
-      <c r="AH13" s="46"/>
-      <c r="AI13" s="46"/>
-      <c r="AJ13" s="46"/>
-      <c r="AK13" s="46"/>
-      <c r="AL13" s="46"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="24"/>
+      <c r="N13" s="24"/>
+      <c r="O13" s="24"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="24"/>
+      <c r="R13" s="24"/>
+      <c r="S13" s="24"/>
+      <c r="T13" s="24"/>
+      <c r="U13" s="24"/>
+      <c r="V13" s="24"/>
+      <c r="W13" s="24"/>
+      <c r="X13" s="24"/>
+      <c r="Y13" s="24"/>
+      <c r="Z13" s="24"/>
+      <c r="AA13" s="24"/>
+      <c r="AB13" s="24"/>
+      <c r="AC13" s="24"/>
+      <c r="AD13" s="24"/>
+      <c r="AE13" s="24"/>
+      <c r="AF13" s="24"/>
+      <c r="AG13" s="24"/>
+      <c r="AH13" s="24"/>
+      <c r="AI13" s="24"/>
+      <c r="AJ13" s="24"/>
+      <c r="AK13" s="24"/>
+      <c r="AL13" s="24"/>
     </row>
     <row r="14" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="46"/>
-      <c r="N14" s="46"/>
-      <c r="O14" s="46"/>
-      <c r="P14" s="46"/>
-      <c r="Q14" s="46"/>
-      <c r="R14" s="46"/>
-      <c r="S14" s="46"/>
-      <c r="T14" s="46"/>
-      <c r="U14" s="46"/>
-      <c r="V14" s="46"/>
-      <c r="W14" s="46"/>
-      <c r="X14" s="46"/>
-      <c r="Y14" s="46"/>
-      <c r="Z14" s="46"/>
-      <c r="AA14" s="46"/>
-      <c r="AB14" s="46"/>
-      <c r="AC14" s="46"/>
-      <c r="AD14" s="46"/>
-      <c r="AE14" s="46"/>
-      <c r="AF14" s="46"/>
-      <c r="AG14" s="46"/>
-      <c r="AH14" s="46"/>
-      <c r="AI14" s="46"/>
-      <c r="AJ14" s="46"/>
-      <c r="AK14" s="46"/>
-      <c r="AL14" s="46"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24"/>
+      <c r="S14" s="24"/>
+      <c r="T14" s="24"/>
+      <c r="U14" s="24"/>
+      <c r="V14" s="24"/>
+      <c r="W14" s="24"/>
+      <c r="X14" s="24"/>
+      <c r="Y14" s="24"/>
+      <c r="Z14" s="24"/>
+      <c r="AA14" s="24"/>
+      <c r="AB14" s="24"/>
+      <c r="AC14" s="24"/>
+      <c r="AD14" s="24"/>
+      <c r="AE14" s="24"/>
+      <c r="AF14" s="24"/>
+      <c r="AG14" s="24"/>
+      <c r="AH14" s="24"/>
+      <c r="AI14" s="24"/>
+      <c r="AJ14" s="24"/>
+      <c r="AK14" s="24"/>
+      <c r="AL14" s="24"/>
     </row>
     <row r="15" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="47"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="48"/>
-      <c r="K15" s="48"/>
-      <c r="L15" s="48"/>
-      <c r="M15" s="48"/>
-      <c r="N15" s="48"/>
-      <c r="O15" s="48"/>
-      <c r="P15" s="48"/>
-      <c r="Q15" s="48"/>
-      <c r="R15" s="48"/>
-      <c r="S15" s="48"/>
-      <c r="T15" s="48"/>
-      <c r="U15" s="48"/>
-      <c r="V15" s="48"/>
-      <c r="W15" s="48"/>
-      <c r="X15" s="48"/>
-      <c r="Y15" s="48"/>
-      <c r="Z15" s="48"/>
-      <c r="AA15" s="48"/>
-      <c r="AB15" s="48"/>
-      <c r="AC15" s="48"/>
-      <c r="AD15" s="48"/>
-      <c r="AE15" s="48"/>
-      <c r="AF15" s="48"/>
-      <c r="AG15" s="48"/>
-      <c r="AH15" s="48"/>
-      <c r="AI15" s="48"/>
-      <c r="AJ15" s="48"/>
-      <c r="AK15" s="48"/>
-      <c r="AL15" s="48"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="26"/>
+      <c r="N15" s="26"/>
+      <c r="O15" s="26"/>
+      <c r="P15" s="26"/>
+      <c r="Q15" s="26"/>
+      <c r="R15" s="26"/>
+      <c r="S15" s="26"/>
+      <c r="T15" s="26"/>
+      <c r="U15" s="26"/>
+      <c r="V15" s="26"/>
+      <c r="W15" s="26"/>
+      <c r="X15" s="26"/>
+      <c r="Y15" s="26"/>
+      <c r="Z15" s="26"/>
+      <c r="AA15" s="26"/>
+      <c r="AB15" s="26"/>
+      <c r="AC15" s="26"/>
+      <c r="AD15" s="26"/>
+      <c r="AE15" s="26"/>
+      <c r="AF15" s="26"/>
+      <c r="AG15" s="26"/>
+      <c r="AH15" s="26"/>
+      <c r="AI15" s="26"/>
+      <c r="AJ15" s="26"/>
+      <c r="AK15" s="26"/>
+      <c r="AL15" s="26"/>
     </row>
     <row r="16" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
@@ -1586,47 +1646,47 @@
     </row>
     <row r="17" spans="1:38" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
-      <c r="B17" s="49" t="s">
+      <c r="B17" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="17" t="s">
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="16"/>
-      <c r="O17" s="16"/>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="16"/>
-      <c r="R17" s="16"/>
-      <c r="S17" s="16"/>
-      <c r="T17" s="16"/>
-      <c r="U17" s="16"/>
-      <c r="V17" s="16"/>
-      <c r="W17" s="16"/>
-      <c r="X17" s="16"/>
-      <c r="Y17" s="16"/>
-      <c r="Z17" s="16"/>
-      <c r="AA17" s="16"/>
-      <c r="AB17" s="16"/>
-      <c r="AC17" s="16"/>
-      <c r="AD17" s="16"/>
-      <c r="AE17" s="16"/>
-      <c r="AF17" s="16"/>
-      <c r="AG17" s="16"/>
-      <c r="AH17" s="16"/>
-      <c r="AI17" s="16"/>
-      <c r="AJ17" s="16"/>
-      <c r="AK17" s="16"/>
-      <c r="AL17" s="16"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="17"/>
+      <c r="S17" s="17"/>
+      <c r="T17" s="17"/>
+      <c r="U17" s="17"/>
+      <c r="V17" s="17"/>
+      <c r="W17" s="17"/>
+      <c r="X17" s="17"/>
+      <c r="Y17" s="17"/>
+      <c r="Z17" s="17"/>
+      <c r="AA17" s="17"/>
+      <c r="AB17" s="17"/>
+      <c r="AC17" s="17"/>
+      <c r="AD17" s="17"/>
+      <c r="AE17" s="17"/>
+      <c r="AF17" s="17"/>
+      <c r="AG17" s="17"/>
+      <c r="AH17" s="17"/>
+      <c r="AI17" s="17"/>
+      <c r="AJ17" s="17"/>
+      <c r="AK17" s="17"/>
+      <c r="AL17" s="17"/>
     </row>
     <row r="18" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
@@ -1670,47 +1730,47 @@
     </row>
     <row r="19" spans="1:38" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
-      <c r="B19" s="49" t="s">
+      <c r="B19" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="17" t="s">
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="16"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="16"/>
-      <c r="R19" s="16"/>
-      <c r="S19" s="16"/>
-      <c r="T19" s="16"/>
-      <c r="U19" s="16"/>
-      <c r="V19" s="16"/>
-      <c r="W19" s="16"/>
-      <c r="X19" s="16"/>
-      <c r="Y19" s="16"/>
-      <c r="Z19" s="16"/>
-      <c r="AA19" s="16"/>
-      <c r="AB19" s="16"/>
-      <c r="AC19" s="16"/>
-      <c r="AD19" s="16"/>
-      <c r="AE19" s="16"/>
-      <c r="AF19" s="16"/>
-      <c r="AG19" s="16"/>
-      <c r="AH19" s="16"/>
-      <c r="AI19" s="16"/>
-      <c r="AJ19" s="16"/>
-      <c r="AK19" s="16"/>
-      <c r="AL19" s="16"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="17"/>
+      <c r="S19" s="17"/>
+      <c r="T19" s="17"/>
+      <c r="U19" s="17"/>
+      <c r="V19" s="17"/>
+      <c r="W19" s="17"/>
+      <c r="X19" s="17"/>
+      <c r="Y19" s="17"/>
+      <c r="Z19" s="17"/>
+      <c r="AA19" s="17"/>
+      <c r="AB19" s="17"/>
+      <c r="AC19" s="17"/>
+      <c r="AD19" s="17"/>
+      <c r="AE19" s="17"/>
+      <c r="AF19" s="17"/>
+      <c r="AG19" s="17"/>
+      <c r="AH19" s="17"/>
+      <c r="AI19" s="17"/>
+      <c r="AJ19" s="17"/>
+      <c r="AK19" s="17"/>
+      <c r="AL19" s="17"/>
     </row>
     <row r="20" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
@@ -1754,160 +1814,160 @@
     </row>
     <row r="21" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="B21" s="50" t="s">
+      <c r="B21" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="19"/>
-      <c r="D21" s="18" t="s">
+      <c r="C21" s="20"/>
+      <c r="D21" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="P21" s="19"/>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="19"/>
-      <c r="S21" s="18" t="s">
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20"/>
+      <c r="R21" s="20"/>
+      <c r="S21" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="T21" s="19"/>
-      <c r="U21" s="19"/>
-      <c r="V21" s="19"/>
-      <c r="W21" s="18" t="s">
+      <c r="T21" s="20"/>
+      <c r="U21" s="20"/>
+      <c r="V21" s="20"/>
+      <c r="W21" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="X21" s="19"/>
-      <c r="Y21" s="19"/>
-      <c r="Z21" s="18" t="s">
+      <c r="X21" s="20"/>
+      <c r="Y21" s="20"/>
+      <c r="Z21" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="AA21" s="19"/>
-      <c r="AB21" s="19"/>
-      <c r="AC21" s="19"/>
-      <c r="AD21" s="19"/>
-      <c r="AE21" s="19"/>
-      <c r="AF21" s="18" t="s">
+      <c r="AA21" s="20"/>
+      <c r="AB21" s="20"/>
+      <c r="AC21" s="20"/>
+      <c r="AD21" s="20"/>
+      <c r="AE21" s="20"/>
+      <c r="AF21" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="AG21" s="19"/>
-      <c r="AH21" s="19"/>
-      <c r="AI21" s="19"/>
-      <c r="AJ21" s="19"/>
-      <c r="AK21" s="51"/>
+      <c r="AG21" s="20"/>
+      <c r="AH21" s="20"/>
+      <c r="AI21" s="20"/>
+      <c r="AJ21" s="20"/>
+      <c r="AK21" s="22"/>
       <c r="AL21" s="1"/>
     </row>
     <row r="22" spans="1:38" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
-      <c r="B22" s="21">
+      <c r="B22" s="44">
         <v>1</v>
       </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="22" t="s">
+      <c r="C22" s="28"/>
+      <c r="D22" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="13"/>
-      <c r="M22" s="13"/>
-      <c r="N22" s="13"/>
-      <c r="O22" s="13"/>
-      <c r="P22" s="13"/>
-      <c r="Q22" s="13"/>
-      <c r="R22" s="13"/>
-      <c r="S22" s="23">
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+      <c r="M22" s="28"/>
+      <c r="N22" s="28"/>
+      <c r="O22" s="28"/>
+      <c r="P22" s="28"/>
+      <c r="Q22" s="28"/>
+      <c r="R22" s="28"/>
+      <c r="S22" s="37">
         <v>1</v>
       </c>
-      <c r="T22" s="24"/>
-      <c r="U22" s="24"/>
-      <c r="V22" s="24"/>
-      <c r="W22" s="25" t="s">
+      <c r="T22" s="36"/>
+      <c r="U22" s="36"/>
+      <c r="V22" s="36"/>
+      <c r="W22" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="X22" s="24"/>
-      <c r="Y22" s="24"/>
-      <c r="Z22" s="12" t="s">
+      <c r="X22" s="36"/>
+      <c r="Y22" s="36"/>
+      <c r="Z22" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="AA22" s="13"/>
-      <c r="AB22" s="13"/>
-      <c r="AC22" s="13"/>
-      <c r="AD22" s="13"/>
-      <c r="AE22" s="13"/>
-      <c r="AF22" s="12" t="e">
+      <c r="AA22" s="28"/>
+      <c r="AB22" s="28"/>
+      <c r="AC22" s="28"/>
+      <c r="AD22" s="28"/>
+      <c r="AE22" s="28"/>
+      <c r="AF22" s="40" t="e">
         <f t="shared" ref="AF22:AF23" si="0">S22*Z22</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG22" s="13"/>
-      <c r="AH22" s="13"/>
-      <c r="AI22" s="13"/>
-      <c r="AJ22" s="13"/>
-      <c r="AK22" s="14"/>
+      <c r="AG22" s="28"/>
+      <c r="AH22" s="28"/>
+      <c r="AI22" s="28"/>
+      <c r="AJ22" s="28"/>
+      <c r="AK22" s="41"/>
       <c r="AL22" s="3"/>
     </row>
     <row r="23" spans="1:38" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="21">
+      <c r="B23" s="44">
         <v>2</v>
       </c>
-      <c r="C23" s="13"/>
-      <c r="D23" s="22" t="s">
+      <c r="C23" s="28"/>
+      <c r="D23" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="13"/>
-      <c r="M23" s="13"/>
-      <c r="N23" s="13"/>
-      <c r="O23" s="13"/>
-      <c r="P23" s="13"/>
-      <c r="Q23" s="13"/>
-      <c r="R23" s="13"/>
-      <c r="S23" s="23">
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="28"/>
+      <c r="N23" s="28"/>
+      <c r="O23" s="28"/>
+      <c r="P23" s="28"/>
+      <c r="Q23" s="28"/>
+      <c r="R23" s="28"/>
+      <c r="S23" s="37">
         <v>1</v>
       </c>
-      <c r="T23" s="24"/>
-      <c r="U23" s="24"/>
-      <c r="V23" s="24"/>
-      <c r="W23" s="25" t="s">
+      <c r="T23" s="36"/>
+      <c r="U23" s="36"/>
+      <c r="V23" s="36"/>
+      <c r="W23" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="X23" s="24"/>
-      <c r="Y23" s="24"/>
-      <c r="Z23" s="12" t="s">
+      <c r="X23" s="36"/>
+      <c r="Y23" s="36"/>
+      <c r="Z23" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="AA23" s="13"/>
-      <c r="AB23" s="13"/>
-      <c r="AC23" s="13"/>
-      <c r="AD23" s="13"/>
-      <c r="AE23" s="13"/>
-      <c r="AF23" s="12" t="e">
+      <c r="AA23" s="28"/>
+      <c r="AB23" s="28"/>
+      <c r="AC23" s="28"/>
+      <c r="AD23" s="28"/>
+      <c r="AE23" s="28"/>
+      <c r="AF23" s="40" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="AG23" s="13"/>
-      <c r="AH23" s="13"/>
-      <c r="AI23" s="13"/>
-      <c r="AJ23" s="13"/>
-      <c r="AK23" s="14"/>
+      <c r="AG23" s="28"/>
+      <c r="AH23" s="28"/>
+      <c r="AI23" s="28"/>
+      <c r="AJ23" s="28"/>
+      <c r="AK23" s="41"/>
       <c r="AL23" s="3"/>
     </row>
     <row r="24" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1984,15 +2044,15 @@
       <c r="AE25" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="AF25" s="20" t="e">
+      <c r="AF25" s="43" t="e">
         <f>SUM(AF22:AK23)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG25" s="16"/>
-      <c r="AH25" s="16"/>
-      <c r="AI25" s="16"/>
-      <c r="AJ25" s="16"/>
-      <c r="AK25" s="16"/>
+      <c r="AG25" s="17"/>
+      <c r="AH25" s="17"/>
+      <c r="AI25" s="17"/>
+      <c r="AJ25" s="17"/>
+      <c r="AK25" s="17"/>
       <c r="AL25" s="1"/>
     </row>
     <row r="26" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -2029,14 +2089,14 @@
       <c r="AE26" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="AF26" s="20" t="s">
+      <c r="AF26" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="AG26" s="16"/>
-      <c r="AH26" s="16"/>
-      <c r="AI26" s="16"/>
-      <c r="AJ26" s="16"/>
-      <c r="AK26" s="16"/>
+      <c r="AG26" s="17"/>
+      <c r="AH26" s="17"/>
+      <c r="AI26" s="17"/>
+      <c r="AJ26" s="17"/>
+      <c r="AK26" s="17"/>
       <c r="AL26" s="1"/>
     </row>
     <row r="27" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -2073,98 +2133,98 @@
       <c r="AE27" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AF27" s="20" t="e">
+      <c r="AF27" s="43" t="e">
         <f>SUM(AF25:AK26)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG27" s="16"/>
-      <c r="AH27" s="16"/>
-      <c r="AI27" s="16"/>
-      <c r="AJ27" s="16"/>
-      <c r="AK27" s="16"/>
+      <c r="AG27" s="17"/>
+      <c r="AH27" s="17"/>
+      <c r="AI27" s="17"/>
+      <c r="AJ27" s="17"/>
+      <c r="AK27" s="17"/>
       <c r="AL27" s="1"/>
     </row>
     <row r="28" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="16"/>
-      <c r="O28" s="16"/>
-      <c r="P28" s="16"/>
-      <c r="Q28" s="16"/>
-      <c r="R28" s="16"/>
-      <c r="S28" s="16"/>
-      <c r="T28" s="16"/>
-      <c r="U28" s="16"/>
-      <c r="V28" s="16"/>
-      <c r="W28" s="16"/>
-      <c r="X28" s="16"/>
-      <c r="Y28" s="16"/>
-      <c r="Z28" s="16"/>
-      <c r="AA28" s="16"/>
-      <c r="AB28" s="16"/>
-      <c r="AC28" s="16"/>
-      <c r="AD28" s="16"/>
-      <c r="AE28" s="16"/>
-      <c r="AF28" s="16"/>
-      <c r="AG28" s="16"/>
-      <c r="AH28" s="16"/>
-      <c r="AI28" s="16"/>
-      <c r="AJ28" s="16"/>
-      <c r="AK28" s="16"/>
-      <c r="AL28" s="16"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="17"/>
+      <c r="S28" s="17"/>
+      <c r="T28" s="17"/>
+      <c r="U28" s="17"/>
+      <c r="V28" s="17"/>
+      <c r="W28" s="17"/>
+      <c r="X28" s="17"/>
+      <c r="Y28" s="17"/>
+      <c r="Z28" s="17"/>
+      <c r="AA28" s="17"/>
+      <c r="AB28" s="17"/>
+      <c r="AC28" s="17"/>
+      <c r="AD28" s="17"/>
+      <c r="AE28" s="17"/>
+      <c r="AF28" s="17"/>
+      <c r="AG28" s="17"/>
+      <c r="AH28" s="17"/>
+      <c r="AI28" s="17"/>
+      <c r="AJ28" s="17"/>
+      <c r="AK28" s="17"/>
+      <c r="AL28" s="17"/>
     </row>
     <row r="29" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="16"/>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="16"/>
-      <c r="O29" s="16"/>
-      <c r="P29" s="16"/>
-      <c r="Q29" s="16"/>
-      <c r="R29" s="16"/>
-      <c r="S29" s="16"/>
-      <c r="T29" s="16"/>
-      <c r="U29" s="16"/>
-      <c r="V29" s="16"/>
-      <c r="W29" s="16"/>
-      <c r="X29" s="16"/>
-      <c r="Y29" s="16"/>
-      <c r="Z29" s="16"/>
-      <c r="AA29" s="16"/>
-      <c r="AB29" s="16"/>
-      <c r="AC29" s="16"/>
-      <c r="AD29" s="16"/>
-      <c r="AE29" s="16"/>
-      <c r="AF29" s="16"/>
-      <c r="AG29" s="16"/>
-      <c r="AH29" s="16"/>
-      <c r="AI29" s="16"/>
-      <c r="AJ29" s="16"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17"/>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="17"/>
+      <c r="S29" s="17"/>
+      <c r="T29" s="17"/>
+      <c r="U29" s="17"/>
+      <c r="V29" s="17"/>
+      <c r="W29" s="17"/>
+      <c r="X29" s="17"/>
+      <c r="Y29" s="17"/>
+      <c r="Z29" s="17"/>
+      <c r="AA29" s="17"/>
+      <c r="AB29" s="17"/>
+      <c r="AC29" s="17"/>
+      <c r="AD29" s="17"/>
+      <c r="AE29" s="17"/>
+      <c r="AF29" s="17"/>
+      <c r="AG29" s="17"/>
+      <c r="AH29" s="17"/>
+      <c r="AI29" s="17"/>
+      <c r="AJ29" s="17"/>
       <c r="AK29" s="3"/>
       <c r="AL29" s="3"/>
     </row>
@@ -2309,23 +2369,23 @@
       <c r="P33" s="8"/>
       <c r="Q33" s="8"/>
       <c r="R33" s="1"/>
-      <c r="S33" s="52" t="s">
+      <c r="S33" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="T33" s="32"/>
-      <c r="U33" s="32"/>
-      <c r="V33" s="32"/>
-      <c r="W33" s="32"/>
-      <c r="X33" s="32"/>
-      <c r="Y33" s="32"/>
-      <c r="Z33" s="32"/>
-      <c r="AA33" s="32"/>
-      <c r="AB33" s="32"/>
-      <c r="AC33" s="32"/>
-      <c r="AD33" s="32"/>
-      <c r="AE33" s="32"/>
-      <c r="AF33" s="32"/>
-      <c r="AG33" s="32"/>
+      <c r="T33" s="13"/>
+      <c r="U33" s="13"/>
+      <c r="V33" s="13"/>
+      <c r="W33" s="13"/>
+      <c r="X33" s="13"/>
+      <c r="Y33" s="13"/>
+      <c r="Z33" s="13"/>
+      <c r="AA33" s="13"/>
+      <c r="AB33" s="13"/>
+      <c r="AC33" s="13"/>
+      <c r="AD33" s="13"/>
+      <c r="AE33" s="13"/>
+      <c r="AF33" s="13"/>
+      <c r="AG33" s="13"/>
       <c r="AH33" s="1"/>
       <c r="AI33" s="1"/>
       <c r="AJ33" s="1"/>
@@ -2342,34 +2402,34 @@
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
       <c r="I34" s="9"/>
-      <c r="J34" s="53" t="s">
+      <c r="J34" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="K34" s="54"/>
-      <c r="L34" s="54"/>
-      <c r="M34" s="54"/>
-      <c r="N34" s="54"/>
-      <c r="O34" s="54"/>
-      <c r="P34" s="54"/>
-      <c r="Q34" s="54"/>
+      <c r="K34" s="15"/>
+      <c r="L34" s="15"/>
+      <c r="M34" s="15"/>
+      <c r="N34" s="15"/>
+      <c r="O34" s="15"/>
+      <c r="P34" s="15"/>
+      <c r="Q34" s="15"/>
       <c r="R34" s="9"/>
-      <c r="S34" s="53" t="s">
+      <c r="S34" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="T34" s="54"/>
-      <c r="U34" s="54"/>
-      <c r="V34" s="54"/>
-      <c r="W34" s="54"/>
-      <c r="X34" s="54"/>
-      <c r="Y34" s="54"/>
-      <c r="Z34" s="54"/>
-      <c r="AA34" s="54"/>
-      <c r="AB34" s="54"/>
-      <c r="AC34" s="54"/>
-      <c r="AD34" s="54"/>
-      <c r="AE34" s="54"/>
-      <c r="AF34" s="54"/>
-      <c r="AG34" s="54"/>
+      <c r="T34" s="15"/>
+      <c r="U34" s="15"/>
+      <c r="V34" s="15"/>
+      <c r="W34" s="15"/>
+      <c r="X34" s="15"/>
+      <c r="Y34" s="15"/>
+      <c r="Z34" s="15"/>
+      <c r="AA34" s="15"/>
+      <c r="AB34" s="15"/>
+      <c r="AC34" s="15"/>
+      <c r="AD34" s="15"/>
+      <c r="AE34" s="15"/>
+      <c r="AF34" s="15"/>
+      <c r="AG34" s="15"/>
       <c r="AH34" s="1"/>
       <c r="AI34" s="1"/>
       <c r="AJ34" s="1"/>
@@ -2437,21 +2497,21 @@
       <c r="P36" s="8"/>
       <c r="Q36" s="8"/>
       <c r="R36" s="1"/>
-      <c r="S36" s="52"/>
-      <c r="T36" s="32"/>
-      <c r="U36" s="32"/>
-      <c r="V36" s="32"/>
-      <c r="W36" s="32"/>
-      <c r="X36" s="32"/>
-      <c r="Y36" s="32"/>
-      <c r="Z36" s="32"/>
-      <c r="AA36" s="32"/>
-      <c r="AB36" s="32"/>
-      <c r="AC36" s="32"/>
-      <c r="AD36" s="32"/>
-      <c r="AE36" s="32"/>
-      <c r="AF36" s="32"/>
-      <c r="AG36" s="32"/>
+      <c r="S36" s="12"/>
+      <c r="T36" s="13"/>
+      <c r="U36" s="13"/>
+      <c r="V36" s="13"/>
+      <c r="W36" s="13"/>
+      <c r="X36" s="13"/>
+      <c r="Y36" s="13"/>
+      <c r="Z36" s="13"/>
+      <c r="AA36" s="13"/>
+      <c r="AB36" s="13"/>
+      <c r="AC36" s="13"/>
+      <c r="AD36" s="13"/>
+      <c r="AE36" s="13"/>
+      <c r="AF36" s="13"/>
+      <c r="AG36" s="13"/>
       <c r="AH36" s="1"/>
       <c r="AI36" s="1"/>
       <c r="AJ36" s="1"/>
@@ -2468,34 +2528,34 @@
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
-      <c r="J37" s="53" t="s">
+      <c r="J37" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="K37" s="54"/>
-      <c r="L37" s="54"/>
-      <c r="M37" s="54"/>
-      <c r="N37" s="54"/>
-      <c r="O37" s="54"/>
-      <c r="P37" s="54"/>
-      <c r="Q37" s="54"/>
+      <c r="K37" s="15"/>
+      <c r="L37" s="15"/>
+      <c r="M37" s="15"/>
+      <c r="N37" s="15"/>
+      <c r="O37" s="15"/>
+      <c r="P37" s="15"/>
+      <c r="Q37" s="15"/>
       <c r="R37" s="9"/>
-      <c r="S37" s="53" t="s">
+      <c r="S37" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="T37" s="54"/>
-      <c r="U37" s="54"/>
-      <c r="V37" s="54"/>
-      <c r="W37" s="54"/>
-      <c r="X37" s="54"/>
-      <c r="Y37" s="54"/>
-      <c r="Z37" s="54"/>
-      <c r="AA37" s="54"/>
-      <c r="AB37" s="54"/>
-      <c r="AC37" s="54"/>
-      <c r="AD37" s="54"/>
-      <c r="AE37" s="54"/>
-      <c r="AF37" s="54"/>
-      <c r="AG37" s="54"/>
+      <c r="T37" s="15"/>
+      <c r="U37" s="15"/>
+      <c r="V37" s="15"/>
+      <c r="W37" s="15"/>
+      <c r="X37" s="15"/>
+      <c r="Y37" s="15"/>
+      <c r="Z37" s="15"/>
+      <c r="AA37" s="15"/>
+      <c r="AB37" s="15"/>
+      <c r="AC37" s="15"/>
+      <c r="AD37" s="15"/>
+      <c r="AE37" s="15"/>
+      <c r="AF37" s="15"/>
+      <c r="AG37" s="15"/>
       <c r="AH37" s="1"/>
       <c r="AI37" s="1"/>
       <c r="AJ37" s="1"/>
@@ -40906,29 +40966,22 @@
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="S33:AG33"/>
-    <mergeCell ref="J34:Q34"/>
-    <mergeCell ref="S34:AG34"/>
-    <mergeCell ref="S36:AG36"/>
-    <mergeCell ref="J37:Q37"/>
-    <mergeCell ref="S37:AG37"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="G19:AL19"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="AF21:AK21"/>
-    <mergeCell ref="D21:R21"/>
-    <mergeCell ref="S21:V21"/>
-    <mergeCell ref="B11:T11"/>
-    <mergeCell ref="B13:AL14"/>
-    <mergeCell ref="B15:AL15"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="G17:AL17"/>
-    <mergeCell ref="B2:T3"/>
-    <mergeCell ref="U2:X2"/>
-    <mergeCell ref="Y2:AL2"/>
-    <mergeCell ref="Y3:AL4"/>
-    <mergeCell ref="B4:T4"/>
-    <mergeCell ref="U3:X4"/>
+    <mergeCell ref="Z23:AE23"/>
+    <mergeCell ref="AF23:AK23"/>
+    <mergeCell ref="B28:AL28"/>
+    <mergeCell ref="B29:AJ29"/>
+    <mergeCell ref="W21:Y21"/>
+    <mergeCell ref="Z21:AE21"/>
+    <mergeCell ref="Z22:AE22"/>
+    <mergeCell ref="AF22:AK22"/>
+    <mergeCell ref="AF25:AK25"/>
+    <mergeCell ref="AF26:AK26"/>
+    <mergeCell ref="AF27:AK27"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:R22"/>
+    <mergeCell ref="S22:V22"/>
+    <mergeCell ref="W22:Y22"/>
+    <mergeCell ref="B23:C23"/>
     <mergeCell ref="W23:Y23"/>
     <mergeCell ref="D23:R23"/>
     <mergeCell ref="S23:V23"/>
@@ -40945,22 +40998,29 @@
     <mergeCell ref="K8:L8"/>
     <mergeCell ref="M8:T8"/>
     <mergeCell ref="B9:T10"/>
-    <mergeCell ref="Z23:AE23"/>
-    <mergeCell ref="AF23:AK23"/>
-    <mergeCell ref="B28:AL28"/>
-    <mergeCell ref="B29:AJ29"/>
-    <mergeCell ref="W21:Y21"/>
-    <mergeCell ref="Z21:AE21"/>
-    <mergeCell ref="Z22:AE22"/>
-    <mergeCell ref="AF22:AK22"/>
-    <mergeCell ref="AF25:AK25"/>
-    <mergeCell ref="AF26:AK26"/>
-    <mergeCell ref="AF27:AK27"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:R22"/>
-    <mergeCell ref="S22:V22"/>
-    <mergeCell ref="W22:Y22"/>
-    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B2:T3"/>
+    <mergeCell ref="U2:X2"/>
+    <mergeCell ref="Y2:AL2"/>
+    <mergeCell ref="Y3:AL4"/>
+    <mergeCell ref="B4:T4"/>
+    <mergeCell ref="U3:X4"/>
+    <mergeCell ref="B11:T11"/>
+    <mergeCell ref="B13:AL14"/>
+    <mergeCell ref="B15:AL15"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="G17:AL17"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="G19:AL19"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="AF21:AK21"/>
+    <mergeCell ref="D21:R21"/>
+    <mergeCell ref="S21:V21"/>
+    <mergeCell ref="S33:AG33"/>
+    <mergeCell ref="J34:Q34"/>
+    <mergeCell ref="S34:AG34"/>
+    <mergeCell ref="S36:AG36"/>
+    <mergeCell ref="J37:Q37"/>
+    <mergeCell ref="S37:AG37"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="97" orientation="portrait" r:id="rId1"/>

--- a/templates/invoice_template_v2.xlsx
+++ b/templates/invoice_template_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Проекты\Агент Авто Континент\01_БОТ_АКТУАЛЬНЫЙ\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13229A1E-40D4-46EF-89C2-7DFBF17ED111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23365E3C-8774-425C-BE16-799BA6771F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -174,7 +174,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
@@ -240,6 +240,27 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -495,7 +516,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -528,31 +549,41 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -561,89 +592,85 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -670,10 +697,10 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1804131" cy="1576024"/>
+    <xdr:ext cx="1768048" cy="1544504"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="image2.png" title="Изображение">
+        <xdr:cNvPr descr="stamp" id="2" name="image2.png" title="Изображение">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
@@ -690,8 +717,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2717164" y="5820410"/>
-          <a:ext cx="1804131" cy="1576024"/>
+          <a:off x="2693457" y="5839883"/>
+          <a:ext cx="1768048" cy="1544504"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -711,7 +738,7 @@
     <xdr:ext cx="1205130" cy="607695"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="image1.png" title="Изображение">
+        <xdr:cNvPr descr="signature" id="3" name="image1.png" title="Изображение">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
@@ -1006,403 +1033,403 @@
     </row>
     <row r="2" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
-      <c r="T2" s="28"/>
-      <c r="U2" s="48" t="s">
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
+      <c r="Q2" s="38"/>
+      <c r="R2" s="38"/>
+      <c r="S2" s="38"/>
+      <c r="T2" s="38"/>
+      <c r="U2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="V2" s="49"/>
-      <c r="W2" s="49"/>
-      <c r="X2" s="52"/>
-      <c r="Y2" s="39" t="s">
+      <c r="V2" s="40"/>
+      <c r="W2" s="40"/>
+      <c r="X2" s="41"/>
+      <c r="Y2" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="Z2" s="28"/>
-      <c r="AA2" s="28"/>
-      <c r="AB2" s="28"/>
-      <c r="AC2" s="28"/>
-      <c r="AD2" s="28"/>
-      <c r="AE2" s="28"/>
-      <c r="AF2" s="28"/>
-      <c r="AG2" s="28"/>
-      <c r="AH2" s="28"/>
-      <c r="AI2" s="28"/>
-      <c r="AJ2" s="28"/>
-      <c r="AK2" s="28"/>
-      <c r="AL2" s="29"/>
+      <c r="Z2" s="38"/>
+      <c r="AA2" s="38"/>
+      <c r="AB2" s="38"/>
+      <c r="AC2" s="38"/>
+      <c r="AD2" s="38"/>
+      <c r="AE2" s="38"/>
+      <c r="AF2" s="38"/>
+      <c r="AG2" s="38"/>
+      <c r="AH2" s="38"/>
+      <c r="AI2" s="38"/>
+      <c r="AJ2" s="38"/>
+      <c r="AK2" s="38"/>
+      <c r="AL2" s="43"/>
     </row>
     <row r="3" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
-      <c r="B3" s="30"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
-      <c r="R3" s="17"/>
-      <c r="S3" s="17"/>
-      <c r="T3" s="45"/>
-      <c r="U3" s="62" t="s">
+      <c r="B3" s="44"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="45"/>
+      <c r="P3" s="45"/>
+      <c r="Q3" s="45"/>
+      <c r="R3" s="45"/>
+      <c r="S3" s="45"/>
+      <c r="T3" s="46"/>
+      <c r="U3" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="V3" s="45"/>
-      <c r="W3" s="45"/>
-      <c r="X3" s="54"/>
-      <c r="Y3" s="61" t="s">
+      <c r="V3" s="46"/>
+      <c r="W3" s="46"/>
+      <c r="X3" s="48"/>
+      <c r="Y3" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="Z3" s="17"/>
-      <c r="AA3" s="17"/>
-      <c r="AB3" s="17"/>
-      <c r="AC3" s="17"/>
-      <c r="AD3" s="17"/>
-      <c r="AE3" s="17"/>
-      <c r="AF3" s="17"/>
-      <c r="AG3" s="17"/>
-      <c r="AH3" s="17"/>
-      <c r="AI3" s="17"/>
-      <c r="AJ3" s="17"/>
-      <c r="AK3" s="17"/>
-      <c r="AL3" s="31"/>
+      <c r="Z3" s="45"/>
+      <c r="AA3" s="45"/>
+      <c r="AB3" s="45"/>
+      <c r="AC3" s="45"/>
+      <c r="AD3" s="45"/>
+      <c r="AE3" s="45"/>
+      <c r="AF3" s="45"/>
+      <c r="AG3" s="45"/>
+      <c r="AH3" s="45"/>
+      <c r="AI3" s="45"/>
+      <c r="AJ3" s="45"/>
+      <c r="AK3" s="45"/>
+      <c r="AL3" s="50"/>
     </row>
     <row r="4" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
-      <c r="S4" s="13"/>
-      <c r="T4" s="13"/>
-      <c r="U4" s="55"/>
-      <c r="V4" s="45"/>
-      <c r="W4" s="45"/>
-      <c r="X4" s="54"/>
-      <c r="Y4" s="13"/>
-      <c r="Z4" s="13"/>
-      <c r="AA4" s="13"/>
-      <c r="AB4" s="13"/>
-      <c r="AC4" s="13"/>
-      <c r="AD4" s="13"/>
-      <c r="AE4" s="13"/>
-      <c r="AF4" s="13"/>
-      <c r="AG4" s="13"/>
-      <c r="AH4" s="13"/>
-      <c r="AI4" s="13"/>
-      <c r="AJ4" s="13"/>
-      <c r="AK4" s="13"/>
-      <c r="AL4" s="33"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="52"/>
+      <c r="M4" s="52"/>
+      <c r="N4" s="52"/>
+      <c r="O4" s="52"/>
+      <c r="P4" s="52"/>
+      <c r="Q4" s="52"/>
+      <c r="R4" s="52"/>
+      <c r="S4" s="52"/>
+      <c r="T4" s="52"/>
+      <c r="U4" s="53"/>
+      <c r="V4" s="46"/>
+      <c r="W4" s="46"/>
+      <c r="X4" s="48"/>
+      <c r="Y4" s="52"/>
+      <c r="Z4" s="52"/>
+      <c r="AA4" s="52"/>
+      <c r="AB4" s="52"/>
+      <c r="AC4" s="52"/>
+      <c r="AD4" s="52"/>
+      <c r="AE4" s="52"/>
+      <c r="AF4" s="52"/>
+      <c r="AG4" s="52"/>
+      <c r="AH4" s="52"/>
+      <c r="AI4" s="52"/>
+      <c r="AJ4" s="52"/>
+      <c r="AK4" s="52"/>
+      <c r="AL4" s="54"/>
     </row>
     <row r="5" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="28"/>
-      <c r="O5" s="28"/>
-      <c r="P5" s="28"/>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="28"/>
-      <c r="S5" s="28"/>
-      <c r="T5" s="28"/>
-      <c r="U5" s="48" t="s">
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
+      <c r="J5" s="38"/>
+      <c r="K5" s="38"/>
+      <c r="L5" s="38"/>
+      <c r="M5" s="38"/>
+      <c r="N5" s="38"/>
+      <c r="O5" s="38"/>
+      <c r="P5" s="38"/>
+      <c r="Q5" s="38"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="38"/>
+      <c r="T5" s="38"/>
+      <c r="U5" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="V5" s="49"/>
-      <c r="W5" s="49"/>
-      <c r="X5" s="52"/>
-      <c r="Y5" s="64" t="s">
+      <c r="V5" s="40"/>
+      <c r="W5" s="40"/>
+      <c r="X5" s="41"/>
+      <c r="Y5" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="Z5" s="28"/>
-      <c r="AA5" s="28"/>
-      <c r="AB5" s="28"/>
-      <c r="AC5" s="28"/>
-      <c r="AD5" s="28"/>
-      <c r="AE5" s="28"/>
-      <c r="AF5" s="28"/>
-      <c r="AG5" s="28"/>
-      <c r="AH5" s="28"/>
-      <c r="AI5" s="28"/>
-      <c r="AJ5" s="28"/>
-      <c r="AK5" s="28"/>
-      <c r="AL5" s="29"/>
+      <c r="Z5" s="38"/>
+      <c r="AA5" s="38"/>
+      <c r="AB5" s="38"/>
+      <c r="AC5" s="38"/>
+      <c r="AD5" s="38"/>
+      <c r="AE5" s="38"/>
+      <c r="AF5" s="38"/>
+      <c r="AG5" s="38"/>
+      <c r="AH5" s="38"/>
+      <c r="AI5" s="38"/>
+      <c r="AJ5" s="38"/>
+      <c r="AK5" s="38"/>
+      <c r="AL5" s="43"/>
     </row>
     <row r="6" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
-      <c r="B6" s="30"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17"/>
-      <c r="S6" s="17"/>
-      <c r="T6" s="45"/>
-      <c r="U6" s="62" t="s">
+      <c r="B6" s="44"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45"/>
+      <c r="M6" s="45"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="45"/>
+      <c r="P6" s="45"/>
+      <c r="Q6" s="45"/>
+      <c r="R6" s="45"/>
+      <c r="S6" s="45"/>
+      <c r="T6" s="46"/>
+      <c r="U6" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="45"/>
-      <c r="W6" s="45"/>
-      <c r="X6" s="54"/>
-      <c r="Y6" s="61" t="s">
+      <c r="V6" s="46"/>
+      <c r="W6" s="46"/>
+      <c r="X6" s="48"/>
+      <c r="Y6" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="Z6" s="17"/>
-      <c r="AA6" s="17"/>
-      <c r="AB6" s="17"/>
-      <c r="AC6" s="17"/>
-      <c r="AD6" s="17"/>
-      <c r="AE6" s="17"/>
-      <c r="AF6" s="17"/>
-      <c r="AG6" s="17"/>
-      <c r="AH6" s="17"/>
-      <c r="AI6" s="17"/>
-      <c r="AJ6" s="17"/>
-      <c r="AK6" s="17"/>
-      <c r="AL6" s="31"/>
+      <c r="Z6" s="45"/>
+      <c r="AA6" s="45"/>
+      <c r="AB6" s="45"/>
+      <c r="AC6" s="45"/>
+      <c r="AD6" s="45"/>
+      <c r="AE6" s="45"/>
+      <c r="AF6" s="45"/>
+      <c r="AG6" s="45"/>
+      <c r="AH6" s="45"/>
+      <c r="AI6" s="45"/>
+      <c r="AJ6" s="45"/>
+      <c r="AK6" s="45"/>
+      <c r="AL6" s="50"/>
     </row>
     <row r="7" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
-      <c r="K7" s="45"/>
-      <c r="L7" s="45"/>
-      <c r="M7" s="45"/>
-      <c r="N7" s="45"/>
-      <c r="O7" s="45"/>
-      <c r="P7" s="45"/>
-      <c r="Q7" s="45"/>
-      <c r="R7" s="45"/>
-      <c r="S7" s="45"/>
-      <c r="T7" s="45"/>
-      <c r="U7" s="63"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="46"/>
+      <c r="J7" s="46"/>
+      <c r="K7" s="46"/>
+      <c r="L7" s="46"/>
+      <c r="M7" s="46"/>
+      <c r="N7" s="46"/>
+      <c r="O7" s="46"/>
+      <c r="P7" s="46"/>
+      <c r="Q7" s="46"/>
+      <c r="R7" s="46"/>
+      <c r="S7" s="46"/>
+      <c r="T7" s="46"/>
+      <c r="U7" s="57"/>
       <c r="V7" s="58"/>
       <c r="W7" s="58"/>
       <c r="X7" s="59"/>
-      <c r="Y7" s="13"/>
-      <c r="Z7" s="13"/>
-      <c r="AA7" s="13"/>
-      <c r="AB7" s="13"/>
-      <c r="AC7" s="13"/>
-      <c r="AD7" s="13"/>
-      <c r="AE7" s="13"/>
-      <c r="AF7" s="13"/>
-      <c r="AG7" s="13"/>
-      <c r="AH7" s="13"/>
-      <c r="AI7" s="13"/>
-      <c r="AJ7" s="13"/>
-      <c r="AK7" s="13"/>
-      <c r="AL7" s="33"/>
+      <c r="Y7" s="52"/>
+      <c r="Z7" s="52"/>
+      <c r="AA7" s="52"/>
+      <c r="AB7" s="52"/>
+      <c r="AC7" s="52"/>
+      <c r="AD7" s="52"/>
+      <c r="AE7" s="52"/>
+      <c r="AF7" s="52"/>
+      <c r="AG7" s="52"/>
+      <c r="AH7" s="52"/>
+      <c r="AI7" s="52"/>
+      <c r="AJ7" s="52"/>
+      <c r="AK7" s="52"/>
+      <c r="AL7" s="54"/>
     </row>
     <row r="8" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
-      <c r="B8" s="48" t="s">
+      <c r="B8" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="50" t="s">
+      <c r="C8" s="40"/>
+      <c r="D8" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="49"/>
-      <c r="K8" s="60" t="s">
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="L8" s="49"/>
-      <c r="M8" s="51"/>
-      <c r="N8" s="49"/>
-      <c r="O8" s="49"/>
-      <c r="P8" s="49"/>
-      <c r="Q8" s="49"/>
-      <c r="R8" s="49"/>
-      <c r="S8" s="49"/>
-      <c r="T8" s="52"/>
-      <c r="U8" s="65" t="s">
+      <c r="L8" s="40"/>
+      <c r="M8" s="62"/>
+      <c r="N8" s="40"/>
+      <c r="O8" s="40"/>
+      <c r="P8" s="40"/>
+      <c r="Q8" s="40"/>
+      <c r="R8" s="40"/>
+      <c r="S8" s="40"/>
+      <c r="T8" s="41"/>
+      <c r="U8" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="V8" s="45"/>
-      <c r="W8" s="45"/>
-      <c r="X8" s="31"/>
-      <c r="Y8" s="38" t="s">
+      <c r="V8" s="46"/>
+      <c r="W8" s="46"/>
+      <c r="X8" s="50"/>
+      <c r="Y8" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="Z8" s="28"/>
-      <c r="AA8" s="28"/>
-      <c r="AB8" s="28"/>
-      <c r="AC8" s="28"/>
-      <c r="AD8" s="28"/>
-      <c r="AE8" s="28"/>
-      <c r="AF8" s="28"/>
-      <c r="AG8" s="28"/>
-      <c r="AH8" s="28"/>
-      <c r="AI8" s="28"/>
-      <c r="AJ8" s="28"/>
-      <c r="AK8" s="28"/>
-      <c r="AL8" s="29"/>
+      <c r="Z8" s="38"/>
+      <c r="AA8" s="38"/>
+      <c r="AB8" s="38"/>
+      <c r="AC8" s="38"/>
+      <c r="AD8" s="38"/>
+      <c r="AE8" s="38"/>
+      <c r="AF8" s="38"/>
+      <c r="AG8" s="38"/>
+      <c r="AH8" s="38"/>
+      <c r="AI8" s="38"/>
+      <c r="AJ8" s="38"/>
+      <c r="AK8" s="38"/>
+      <c r="AL8" s="43"/>
     </row>
     <row r="9" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
-      <c r="B9" s="53" t="s">
+      <c r="B9" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="45"/>
-      <c r="K9" s="45"/>
-      <c r="L9" s="45"/>
-      <c r="M9" s="45"/>
-      <c r="N9" s="45"/>
-      <c r="O9" s="45"/>
-      <c r="P9" s="45"/>
-      <c r="Q9" s="45"/>
-      <c r="R9" s="45"/>
-      <c r="S9" s="45"/>
-      <c r="T9" s="54"/>
-      <c r="U9" s="45"/>
-      <c r="V9" s="17"/>
-      <c r="W9" s="17"/>
-      <c r="X9" s="31"/>
-      <c r="Y9" s="30"/>
-      <c r="Z9" s="17"/>
-      <c r="AA9" s="17"/>
-      <c r="AB9" s="17"/>
-      <c r="AC9" s="17"/>
-      <c r="AD9" s="17"/>
-      <c r="AE9" s="17"/>
-      <c r="AF9" s="17"/>
-      <c r="AG9" s="17"/>
-      <c r="AH9" s="17"/>
-      <c r="AI9" s="17"/>
-      <c r="AJ9" s="17"/>
-      <c r="AK9" s="17"/>
-      <c r="AL9" s="31"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
+      <c r="J9" s="46"/>
+      <c r="K9" s="46"/>
+      <c r="L9" s="46"/>
+      <c r="M9" s="46"/>
+      <c r="N9" s="46"/>
+      <c r="O9" s="46"/>
+      <c r="P9" s="46"/>
+      <c r="Q9" s="46"/>
+      <c r="R9" s="46"/>
+      <c r="S9" s="46"/>
+      <c r="T9" s="48"/>
+      <c r="U9" s="46"/>
+      <c r="V9" s="45"/>
+      <c r="W9" s="45"/>
+      <c r="X9" s="50"/>
+      <c r="Y9" s="44"/>
+      <c r="Z9" s="45"/>
+      <c r="AA9" s="45"/>
+      <c r="AB9" s="45"/>
+      <c r="AC9" s="45"/>
+      <c r="AD9" s="45"/>
+      <c r="AE9" s="45"/>
+      <c r="AF9" s="45"/>
+      <c r="AG9" s="45"/>
+      <c r="AH9" s="45"/>
+      <c r="AI9" s="45"/>
+      <c r="AJ9" s="45"/>
+      <c r="AK9" s="45"/>
+      <c r="AL9" s="50"/>
     </row>
     <row r="10" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
-      <c r="B10" s="55"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="46"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="46"/>
-      <c r="M10" s="46"/>
-      <c r="N10" s="46"/>
-      <c r="O10" s="46"/>
-      <c r="P10" s="46"/>
-      <c r="Q10" s="46"/>
-      <c r="R10" s="46"/>
-      <c r="S10" s="46"/>
-      <c r="T10" s="56"/>
-      <c r="U10" s="45"/>
-      <c r="V10" s="17"/>
-      <c r="W10" s="17"/>
-      <c r="X10" s="31"/>
-      <c r="Y10" s="30"/>
-      <c r="Z10" s="17"/>
-      <c r="AA10" s="17"/>
-      <c r="AB10" s="17"/>
-      <c r="AC10" s="17"/>
-      <c r="AD10" s="17"/>
-      <c r="AE10" s="17"/>
-      <c r="AF10" s="17"/>
-      <c r="AG10" s="17"/>
-      <c r="AH10" s="17"/>
-      <c r="AI10" s="17"/>
-      <c r="AJ10" s="17"/>
-      <c r="AK10" s="17"/>
-      <c r="AL10" s="31"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="66"/>
+      <c r="J10" s="66"/>
+      <c r="K10" s="66"/>
+      <c r="L10" s="66"/>
+      <c r="M10" s="66"/>
+      <c r="N10" s="66"/>
+      <c r="O10" s="66"/>
+      <c r="P10" s="66"/>
+      <c r="Q10" s="66"/>
+      <c r="R10" s="66"/>
+      <c r="S10" s="66"/>
+      <c r="T10" s="67"/>
+      <c r="U10" s="46"/>
+      <c r="V10" s="45"/>
+      <c r="W10" s="45"/>
+      <c r="X10" s="50"/>
+      <c r="Y10" s="44"/>
+      <c r="Z10" s="45"/>
+      <c r="AA10" s="45"/>
+      <c r="AB10" s="45"/>
+      <c r="AC10" s="45"/>
+      <c r="AD10" s="45"/>
+      <c r="AE10" s="45"/>
+      <c r="AF10" s="45"/>
+      <c r="AG10" s="45"/>
+      <c r="AH10" s="45"/>
+      <c r="AI10" s="45"/>
+      <c r="AJ10" s="45"/>
+      <c r="AK10" s="45"/>
+      <c r="AL10" s="50"/>
     </row>
     <row r="11" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="57" t="s">
+      <c r="B11" s="68" t="s">
         <v>14</v>
       </c>
       <c r="C11" s="58"/>
@@ -1423,24 +1450,24 @@
       <c r="R11" s="58"/>
       <c r="S11" s="58"/>
       <c r="T11" s="59"/>
-      <c r="U11" s="13"/>
-      <c r="V11" s="13"/>
-      <c r="W11" s="13"/>
-      <c r="X11" s="33"/>
-      <c r="Y11" s="32"/>
-      <c r="Z11" s="13"/>
-      <c r="AA11" s="13"/>
-      <c r="AB11" s="13"/>
-      <c r="AC11" s="13"/>
-      <c r="AD11" s="13"/>
-      <c r="AE11" s="13"/>
-      <c r="AF11" s="13"/>
-      <c r="AG11" s="13"/>
-      <c r="AH11" s="13"/>
-      <c r="AI11" s="13"/>
-      <c r="AJ11" s="13"/>
-      <c r="AK11" s="13"/>
-      <c r="AL11" s="33"/>
+      <c r="U11" s="52"/>
+      <c r="V11" s="52"/>
+      <c r="W11" s="52"/>
+      <c r="X11" s="54"/>
+      <c r="Y11" s="69"/>
+      <c r="Z11" s="52"/>
+      <c r="AA11" s="52"/>
+      <c r="AB11" s="52"/>
+      <c r="AC11" s="52"/>
+      <c r="AD11" s="52"/>
+      <c r="AE11" s="52"/>
+      <c r="AF11" s="52"/>
+      <c r="AG11" s="52"/>
+      <c r="AH11" s="52"/>
+      <c r="AI11" s="52"/>
+      <c r="AJ11" s="52"/>
+      <c r="AK11" s="52"/>
+      <c r="AL11" s="54"/>
     </row>
     <row r="12" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
@@ -1484,125 +1511,125 @@
     </row>
     <row r="13" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="24"/>
-      <c r="M13" s="24"/>
-      <c r="N13" s="24"/>
-      <c r="O13" s="24"/>
-      <c r="P13" s="24"/>
-      <c r="Q13" s="24"/>
-      <c r="R13" s="24"/>
-      <c r="S13" s="24"/>
-      <c r="T13" s="24"/>
-      <c r="U13" s="24"/>
-      <c r="V13" s="24"/>
-      <c r="W13" s="24"/>
-      <c r="X13" s="24"/>
-      <c r="Y13" s="24"/>
-      <c r="Z13" s="24"/>
-      <c r="AA13" s="24"/>
-      <c r="AB13" s="24"/>
-      <c r="AC13" s="24"/>
-      <c r="AD13" s="24"/>
-      <c r="AE13" s="24"/>
-      <c r="AF13" s="24"/>
-      <c r="AG13" s="24"/>
-      <c r="AH13" s="24"/>
-      <c r="AI13" s="24"/>
-      <c r="AJ13" s="24"/>
-      <c r="AK13" s="24"/>
-      <c r="AL13" s="24"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="28"/>
+      <c r="N13" s="28"/>
+      <c r="O13" s="28"/>
+      <c r="P13" s="28"/>
+      <c r="Q13" s="28"/>
+      <c r="R13" s="28"/>
+      <c r="S13" s="28"/>
+      <c r="T13" s="28"/>
+      <c r="U13" s="28"/>
+      <c r="V13" s="28"/>
+      <c r="W13" s="28"/>
+      <c r="X13" s="28"/>
+      <c r="Y13" s="28"/>
+      <c r="Z13" s="28"/>
+      <c r="AA13" s="28"/>
+      <c r="AB13" s="28"/>
+      <c r="AC13" s="28"/>
+      <c r="AD13" s="28"/>
+      <c r="AE13" s="28"/>
+      <c r="AF13" s="28"/>
+      <c r="AG13" s="28"/>
+      <c r="AH13" s="28"/>
+      <c r="AI13" s="28"/>
+      <c r="AJ13" s="28"/>
+      <c r="AK13" s="28"/>
+      <c r="AL13" s="28"/>
     </row>
     <row r="14" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="24"/>
-      <c r="N14" s="24"/>
-      <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="24"/>
-      <c r="R14" s="24"/>
-      <c r="S14" s="24"/>
-      <c r="T14" s="24"/>
-      <c r="U14" s="24"/>
-      <c r="V14" s="24"/>
-      <c r="W14" s="24"/>
-      <c r="X14" s="24"/>
-      <c r="Y14" s="24"/>
-      <c r="Z14" s="24"/>
-      <c r="AA14" s="24"/>
-      <c r="AB14" s="24"/>
-      <c r="AC14" s="24"/>
-      <c r="AD14" s="24"/>
-      <c r="AE14" s="24"/>
-      <c r="AF14" s="24"/>
-      <c r="AG14" s="24"/>
-      <c r="AH14" s="24"/>
-      <c r="AI14" s="24"/>
-      <c r="AJ14" s="24"/>
-      <c r="AK14" s="24"/>
-      <c r="AL14" s="24"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28"/>
+      <c r="M14" s="28"/>
+      <c r="N14" s="28"/>
+      <c r="O14" s="28"/>
+      <c r="P14" s="28"/>
+      <c r="Q14" s="28"/>
+      <c r="R14" s="28"/>
+      <c r="S14" s="28"/>
+      <c r="T14" s="28"/>
+      <c r="U14" s="28"/>
+      <c r="V14" s="28"/>
+      <c r="W14" s="28"/>
+      <c r="X14" s="28"/>
+      <c r="Y14" s="28"/>
+      <c r="Z14" s="28"/>
+      <c r="AA14" s="28"/>
+      <c r="AB14" s="28"/>
+      <c r="AC14" s="28"/>
+      <c r="AD14" s="28"/>
+      <c r="AE14" s="28"/>
+      <c r="AF14" s="28"/>
+      <c r="AG14" s="28"/>
+      <c r="AH14" s="28"/>
+      <c r="AI14" s="28"/>
+      <c r="AJ14" s="28"/>
+      <c r="AK14" s="28"/>
+      <c r="AL14" s="28"/>
     </row>
     <row r="15" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
-      <c r="K15" s="26"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="26"/>
-      <c r="N15" s="26"/>
-      <c r="O15" s="26"/>
-      <c r="P15" s="26"/>
-      <c r="Q15" s="26"/>
-      <c r="R15" s="26"/>
-      <c r="S15" s="26"/>
-      <c r="T15" s="26"/>
-      <c r="U15" s="26"/>
-      <c r="V15" s="26"/>
-      <c r="W15" s="26"/>
-      <c r="X15" s="26"/>
-      <c r="Y15" s="26"/>
-      <c r="Z15" s="26"/>
-      <c r="AA15" s="26"/>
-      <c r="AB15" s="26"/>
-      <c r="AC15" s="26"/>
-      <c r="AD15" s="26"/>
-      <c r="AE15" s="26"/>
-      <c r="AF15" s="26"/>
-      <c r="AG15" s="26"/>
-      <c r="AH15" s="26"/>
-      <c r="AI15" s="26"/>
-      <c r="AJ15" s="26"/>
-      <c r="AK15" s="26"/>
-      <c r="AL15" s="26"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="30"/>
+      <c r="N15" s="30"/>
+      <c r="O15" s="30"/>
+      <c r="P15" s="30"/>
+      <c r="Q15" s="30"/>
+      <c r="R15" s="30"/>
+      <c r="S15" s="30"/>
+      <c r="T15" s="30"/>
+      <c r="U15" s="30"/>
+      <c r="V15" s="30"/>
+      <c r="W15" s="30"/>
+      <c r="X15" s="30"/>
+      <c r="Y15" s="30"/>
+      <c r="Z15" s="30"/>
+      <c r="AA15" s="30"/>
+      <c r="AB15" s="30"/>
+      <c r="AC15" s="30"/>
+      <c r="AD15" s="30"/>
+      <c r="AE15" s="30"/>
+      <c r="AF15" s="30"/>
+      <c r="AG15" s="30"/>
+      <c r="AH15" s="30"/>
+      <c r="AI15" s="30"/>
+      <c r="AJ15" s="30"/>
+      <c r="AK15" s="30"/>
+      <c r="AL15" s="30"/>
     </row>
     <row r="16" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
@@ -1646,47 +1673,47 @@
     </row>
     <row r="17" spans="1:38" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="18" t="s">
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="17"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="17"/>
-      <c r="S17" s="17"/>
-      <c r="T17" s="17"/>
-      <c r="U17" s="17"/>
-      <c r="V17" s="17"/>
-      <c r="W17" s="17"/>
-      <c r="X17" s="17"/>
-      <c r="Y17" s="17"/>
-      <c r="Z17" s="17"/>
-      <c r="AA17" s="17"/>
-      <c r="AB17" s="17"/>
-      <c r="AC17" s="17"/>
-      <c r="AD17" s="17"/>
-      <c r="AE17" s="17"/>
-      <c r="AF17" s="17"/>
-      <c r="AG17" s="17"/>
-      <c r="AH17" s="17"/>
-      <c r="AI17" s="17"/>
-      <c r="AJ17" s="17"/>
-      <c r="AK17" s="17"/>
-      <c r="AL17" s="17"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="16"/>
+      <c r="O17" s="16"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="16"/>
+      <c r="R17" s="16"/>
+      <c r="S17" s="16"/>
+      <c r="T17" s="16"/>
+      <c r="U17" s="16"/>
+      <c r="V17" s="16"/>
+      <c r="W17" s="16"/>
+      <c r="X17" s="16"/>
+      <c r="Y17" s="16"/>
+      <c r="Z17" s="16"/>
+      <c r="AA17" s="16"/>
+      <c r="AB17" s="16"/>
+      <c r="AC17" s="16"/>
+      <c r="AD17" s="16"/>
+      <c r="AE17" s="16"/>
+      <c r="AF17" s="16"/>
+      <c r="AG17" s="16"/>
+      <c r="AH17" s="16"/>
+      <c r="AI17" s="16"/>
+      <c r="AJ17" s="16"/>
+      <c r="AK17" s="16"/>
+      <c r="AL17" s="16"/>
     </row>
     <row r="18" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
@@ -1730,47 +1757,47 @@
     </row>
     <row r="19" spans="1:38" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="18" t="s">
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="17"/>
-      <c r="O19" s="17"/>
-      <c r="P19" s="17"/>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="17"/>
-      <c r="S19" s="17"/>
-      <c r="T19" s="17"/>
-      <c r="U19" s="17"/>
-      <c r="V19" s="17"/>
-      <c r="W19" s="17"/>
-      <c r="X19" s="17"/>
-      <c r="Y19" s="17"/>
-      <c r="Z19" s="17"/>
-      <c r="AA19" s="17"/>
-      <c r="AB19" s="17"/>
-      <c r="AC19" s="17"/>
-      <c r="AD19" s="17"/>
-      <c r="AE19" s="17"/>
-      <c r="AF19" s="17"/>
-      <c r="AG19" s="17"/>
-      <c r="AH19" s="17"/>
-      <c r="AI19" s="17"/>
-      <c r="AJ19" s="17"/>
-      <c r="AK19" s="17"/>
-      <c r="AL19" s="17"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="16"/>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="16"/>
+      <c r="R19" s="16"/>
+      <c r="S19" s="16"/>
+      <c r="T19" s="16"/>
+      <c r="U19" s="16"/>
+      <c r="V19" s="16"/>
+      <c r="W19" s="16"/>
+      <c r="X19" s="16"/>
+      <c r="Y19" s="16"/>
+      <c r="Z19" s="16"/>
+      <c r="AA19" s="16"/>
+      <c r="AB19" s="16"/>
+      <c r="AC19" s="16"/>
+      <c r="AD19" s="16"/>
+      <c r="AE19" s="16"/>
+      <c r="AF19" s="16"/>
+      <c r="AG19" s="16"/>
+      <c r="AH19" s="16"/>
+      <c r="AI19" s="16"/>
+      <c r="AJ19" s="16"/>
+      <c r="AK19" s="16"/>
+      <c r="AL19" s="16"/>
     </row>
     <row r="20" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
@@ -1814,160 +1841,160 @@
     </row>
     <row r="21" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="20"/>
-      <c r="D21" s="21" t="s">
+      <c r="C21" s="19"/>
+      <c r="D21" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
-      <c r="O21" s="20"/>
-      <c r="P21" s="20"/>
-      <c r="Q21" s="20"/>
-      <c r="R21" s="20"/>
-      <c r="S21" s="21" t="s">
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="19"/>
+      <c r="P21" s="19"/>
+      <c r="Q21" s="19"/>
+      <c r="R21" s="19"/>
+      <c r="S21" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="T21" s="20"/>
-      <c r="U21" s="20"/>
-      <c r="V21" s="20"/>
-      <c r="W21" s="21" t="s">
+      <c r="T21" s="19"/>
+      <c r="U21" s="19"/>
+      <c r="V21" s="19"/>
+      <c r="W21" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="X21" s="20"/>
-      <c r="Y21" s="20"/>
-      <c r="Z21" s="21" t="s">
+      <c r="X21" s="19"/>
+      <c r="Y21" s="19"/>
+      <c r="Z21" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="AA21" s="20"/>
-      <c r="AB21" s="20"/>
-      <c r="AC21" s="20"/>
-      <c r="AD21" s="20"/>
-      <c r="AE21" s="20"/>
-      <c r="AF21" s="21" t="s">
+      <c r="AA21" s="19"/>
+      <c r="AB21" s="19"/>
+      <c r="AC21" s="19"/>
+      <c r="AD21" s="19"/>
+      <c r="AE21" s="19"/>
+      <c r="AF21" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="AG21" s="20"/>
-      <c r="AH21" s="20"/>
-      <c r="AI21" s="20"/>
-      <c r="AJ21" s="20"/>
-      <c r="AK21" s="22"/>
+      <c r="AG21" s="19"/>
+      <c r="AH21" s="19"/>
+      <c r="AI21" s="19"/>
+      <c r="AJ21" s="19"/>
+      <c r="AK21" s="33"/>
       <c r="AL21" s="1"/>
     </row>
     <row r="22" spans="1:38" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
-      <c r="B22" s="44">
+      <c r="B22" s="21">
         <v>1</v>
       </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="27" t="s">
+      <c r="C22" s="13"/>
+      <c r="D22" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="28"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="28"/>
-      <c r="M22" s="28"/>
-      <c r="N22" s="28"/>
-      <c r="O22" s="28"/>
-      <c r="P22" s="28"/>
-      <c r="Q22" s="28"/>
-      <c r="R22" s="28"/>
-      <c r="S22" s="37">
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="13"/>
+      <c r="S22" s="23">
         <v>1</v>
       </c>
-      <c r="T22" s="36"/>
-      <c r="U22" s="36"/>
-      <c r="V22" s="36"/>
-      <c r="W22" s="35" t="s">
+      <c r="T22" s="24"/>
+      <c r="U22" s="24"/>
+      <c r="V22" s="24"/>
+      <c r="W22" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="X22" s="36"/>
-      <c r="Y22" s="36"/>
-      <c r="Z22" s="40" t="s">
+      <c r="X22" s="24"/>
+      <c r="Y22" s="24"/>
+      <c r="Z22" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="AA22" s="28"/>
-      <c r="AB22" s="28"/>
-      <c r="AC22" s="28"/>
-      <c r="AD22" s="28"/>
-      <c r="AE22" s="28"/>
-      <c r="AF22" s="40" t="e">
+      <c r="AA22" s="13"/>
+      <c r="AB22" s="13"/>
+      <c r="AC22" s="13"/>
+      <c r="AD22" s="13"/>
+      <c r="AE22" s="13"/>
+      <c r="AF22" s="12" t="e">
         <f t="shared" ref="AF22:AF23" si="0">S22*Z22</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG22" s="28"/>
-      <c r="AH22" s="28"/>
-      <c r="AI22" s="28"/>
-      <c r="AJ22" s="28"/>
-      <c r="AK22" s="41"/>
+      <c r="AG22" s="13"/>
+      <c r="AH22" s="13"/>
+      <c r="AI22" s="13"/>
+      <c r="AJ22" s="13"/>
+      <c r="AK22" s="14"/>
       <c r="AL22" s="3"/>
     </row>
     <row r="23" spans="1:38" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="44">
+      <c r="B23" s="21">
         <v>2</v>
       </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="27" t="s">
+      <c r="C23" s="13"/>
+      <c r="D23" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="28"/>
-      <c r="N23" s="28"/>
-      <c r="O23" s="28"/>
-      <c r="P23" s="28"/>
-      <c r="Q23" s="28"/>
-      <c r="R23" s="28"/>
-      <c r="S23" s="37">
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13"/>
+      <c r="P23" s="13"/>
+      <c r="Q23" s="13"/>
+      <c r="R23" s="13"/>
+      <c r="S23" s="23">
         <v>1</v>
       </c>
-      <c r="T23" s="36"/>
-      <c r="U23" s="36"/>
-      <c r="V23" s="36"/>
-      <c r="W23" s="35" t="s">
+      <c r="T23" s="24"/>
+      <c r="U23" s="24"/>
+      <c r="V23" s="24"/>
+      <c r="W23" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="X23" s="36"/>
-      <c r="Y23" s="36"/>
-      <c r="Z23" s="40" t="s">
+      <c r="X23" s="24"/>
+      <c r="Y23" s="24"/>
+      <c r="Z23" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="AA23" s="28"/>
-      <c r="AB23" s="28"/>
-      <c r="AC23" s="28"/>
-      <c r="AD23" s="28"/>
-      <c r="AE23" s="28"/>
-      <c r="AF23" s="40" t="e">
+      <c r="AA23" s="13"/>
+      <c r="AB23" s="13"/>
+      <c r="AC23" s="13"/>
+      <c r="AD23" s="13"/>
+      <c r="AE23" s="13"/>
+      <c r="AF23" s="12" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="AG23" s="28"/>
-      <c r="AH23" s="28"/>
-      <c r="AI23" s="28"/>
-      <c r="AJ23" s="28"/>
-      <c r="AK23" s="41"/>
+      <c r="AG23" s="13"/>
+      <c r="AH23" s="13"/>
+      <c r="AI23" s="13"/>
+      <c r="AJ23" s="13"/>
+      <c r="AK23" s="14"/>
       <c r="AL23" s="3"/>
     </row>
     <row r="24" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2044,15 +2071,15 @@
       <c r="AE25" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="AF25" s="43" t="e">
+      <c r="AF25" s="20" t="e">
         <f>SUM(AF22:AK23)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG25" s="17"/>
-      <c r="AH25" s="17"/>
-      <c r="AI25" s="17"/>
-      <c r="AJ25" s="17"/>
-      <c r="AK25" s="17"/>
+      <c r="AG25" s="16"/>
+      <c r="AH25" s="16"/>
+      <c r="AI25" s="16"/>
+      <c r="AJ25" s="16"/>
+      <c r="AK25" s="16"/>
       <c r="AL25" s="1"/>
     </row>
     <row r="26" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -2089,14 +2116,14 @@
       <c r="AE26" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="AF26" s="43" t="s">
+      <c r="AF26" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="AG26" s="17"/>
-      <c r="AH26" s="17"/>
-      <c r="AI26" s="17"/>
-      <c r="AJ26" s="17"/>
-      <c r="AK26" s="17"/>
+      <c r="AG26" s="16"/>
+      <c r="AH26" s="16"/>
+      <c r="AI26" s="16"/>
+      <c r="AJ26" s="16"/>
+      <c r="AK26" s="16"/>
       <c r="AL26" s="1"/>
     </row>
     <row r="27" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -2133,98 +2160,98 @@
       <c r="AE27" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AF27" s="43" t="e">
+      <c r="AF27" s="20" t="e">
         <f>SUM(AF25:AK26)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG27" s="17"/>
-      <c r="AH27" s="17"/>
-      <c r="AI27" s="17"/>
-      <c r="AJ27" s="17"/>
-      <c r="AK27" s="17"/>
+      <c r="AG27" s="16"/>
+      <c r="AH27" s="16"/>
+      <c r="AI27" s="16"/>
+      <c r="AJ27" s="16"/>
+      <c r="AK27" s="16"/>
       <c r="AL27" s="1"/>
     </row>
     <row r="28" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="42" t="s">
+      <c r="B28" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="17"/>
-      <c r="N28" s="17"/>
-      <c r="O28" s="17"/>
-      <c r="P28" s="17"/>
-      <c r="Q28" s="17"/>
-      <c r="R28" s="17"/>
-      <c r="S28" s="17"/>
-      <c r="T28" s="17"/>
-      <c r="U28" s="17"/>
-      <c r="V28" s="17"/>
-      <c r="W28" s="17"/>
-      <c r="X28" s="17"/>
-      <c r="Y28" s="17"/>
-      <c r="Z28" s="17"/>
-      <c r="AA28" s="17"/>
-      <c r="AB28" s="17"/>
-      <c r="AC28" s="17"/>
-      <c r="AD28" s="17"/>
-      <c r="AE28" s="17"/>
-      <c r="AF28" s="17"/>
-      <c r="AG28" s="17"/>
-      <c r="AH28" s="17"/>
-      <c r="AI28" s="17"/>
-      <c r="AJ28" s="17"/>
-      <c r="AK28" s="17"/>
-      <c r="AL28" s="17"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="16"/>
+      <c r="N28" s="16"/>
+      <c r="O28" s="16"/>
+      <c r="P28" s="16"/>
+      <c r="Q28" s="16"/>
+      <c r="R28" s="16"/>
+      <c r="S28" s="16"/>
+      <c r="T28" s="16"/>
+      <c r="U28" s="16"/>
+      <c r="V28" s="16"/>
+      <c r="W28" s="16"/>
+      <c r="X28" s="16"/>
+      <c r="Y28" s="16"/>
+      <c r="Z28" s="16"/>
+      <c r="AA28" s="16"/>
+      <c r="AB28" s="16"/>
+      <c r="AC28" s="16"/>
+      <c r="AD28" s="16"/>
+      <c r="AE28" s="16"/>
+      <c r="AF28" s="16"/>
+      <c r="AG28" s="16"/>
+      <c r="AH28" s="16"/>
+      <c r="AI28" s="16"/>
+      <c r="AJ28" s="16"/>
+      <c r="AK28" s="16"/>
+      <c r="AL28" s="16"/>
     </row>
     <row r="29" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
-      <c r="M29" s="17"/>
-      <c r="N29" s="17"/>
-      <c r="O29" s="17"/>
-      <c r="P29" s="17"/>
-      <c r="Q29" s="17"/>
-      <c r="R29" s="17"/>
-      <c r="S29" s="17"/>
-      <c r="T29" s="17"/>
-      <c r="U29" s="17"/>
-      <c r="V29" s="17"/>
-      <c r="W29" s="17"/>
-      <c r="X29" s="17"/>
-      <c r="Y29" s="17"/>
-      <c r="Z29" s="17"/>
-      <c r="AA29" s="17"/>
-      <c r="AB29" s="17"/>
-      <c r="AC29" s="17"/>
-      <c r="AD29" s="17"/>
-      <c r="AE29" s="17"/>
-      <c r="AF29" s="17"/>
-      <c r="AG29" s="17"/>
-      <c r="AH29" s="17"/>
-      <c r="AI29" s="17"/>
-      <c r="AJ29" s="17"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="16"/>
+      <c r="K29" s="16"/>
+      <c r="L29" s="16"/>
+      <c r="M29" s="16"/>
+      <c r="N29" s="16"/>
+      <c r="O29" s="16"/>
+      <c r="P29" s="16"/>
+      <c r="Q29" s="16"/>
+      <c r="R29" s="16"/>
+      <c r="S29" s="16"/>
+      <c r="T29" s="16"/>
+      <c r="U29" s="16"/>
+      <c r="V29" s="16"/>
+      <c r="W29" s="16"/>
+      <c r="X29" s="16"/>
+      <c r="Y29" s="16"/>
+      <c r="Z29" s="16"/>
+      <c r="AA29" s="16"/>
+      <c r="AB29" s="16"/>
+      <c r="AC29" s="16"/>
+      <c r="AD29" s="16"/>
+      <c r="AE29" s="16"/>
+      <c r="AF29" s="16"/>
+      <c r="AG29" s="16"/>
+      <c r="AH29" s="16"/>
+      <c r="AI29" s="16"/>
+      <c r="AJ29" s="16"/>
       <c r="AK29" s="3"/>
       <c r="AL29" s="3"/>
     </row>
@@ -2369,23 +2396,23 @@
       <c r="P33" s="8"/>
       <c r="Q33" s="8"/>
       <c r="R33" s="1"/>
-      <c r="S33" s="12" t="s">
+      <c r="S33" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="T33" s="13"/>
-      <c r="U33" s="13"/>
-      <c r="V33" s="13"/>
-      <c r="W33" s="13"/>
-      <c r="X33" s="13"/>
-      <c r="Y33" s="13"/>
-      <c r="Z33" s="13"/>
-      <c r="AA33" s="13"/>
-      <c r="AB33" s="13"/>
-      <c r="AC33" s="13"/>
-      <c r="AD33" s="13"/>
-      <c r="AE33" s="13"/>
-      <c r="AF33" s="13"/>
-      <c r="AG33" s="13"/>
+      <c r="T33" s="26"/>
+      <c r="U33" s="26"/>
+      <c r="V33" s="26"/>
+      <c r="W33" s="26"/>
+      <c r="X33" s="26"/>
+      <c r="Y33" s="26"/>
+      <c r="Z33" s="26"/>
+      <c r="AA33" s="26"/>
+      <c r="AB33" s="26"/>
+      <c r="AC33" s="26"/>
+      <c r="AD33" s="26"/>
+      <c r="AE33" s="26"/>
+      <c r="AF33" s="26"/>
+      <c r="AG33" s="26"/>
       <c r="AH33" s="1"/>
       <c r="AI33" s="1"/>
       <c r="AJ33" s="1"/>
@@ -2402,34 +2429,34 @@
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
       <c r="I34" s="9"/>
-      <c r="J34" s="14" t="s">
+      <c r="J34" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="K34" s="15"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15"/>
-      <c r="N34" s="15"/>
-      <c r="O34" s="15"/>
-      <c r="P34" s="15"/>
-      <c r="Q34" s="15"/>
+      <c r="K34" s="36"/>
+      <c r="L34" s="36"/>
+      <c r="M34" s="36"/>
+      <c r="N34" s="36"/>
+      <c r="O34" s="36"/>
+      <c r="P34" s="36"/>
+      <c r="Q34" s="36"/>
       <c r="R34" s="9"/>
-      <c r="S34" s="14" t="s">
+      <c r="S34" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="T34" s="15"/>
-      <c r="U34" s="15"/>
-      <c r="V34" s="15"/>
-      <c r="W34" s="15"/>
-      <c r="X34" s="15"/>
-      <c r="Y34" s="15"/>
-      <c r="Z34" s="15"/>
-      <c r="AA34" s="15"/>
-      <c r="AB34" s="15"/>
-      <c r="AC34" s="15"/>
-      <c r="AD34" s="15"/>
-      <c r="AE34" s="15"/>
-      <c r="AF34" s="15"/>
-      <c r="AG34" s="15"/>
+      <c r="T34" s="36"/>
+      <c r="U34" s="36"/>
+      <c r="V34" s="36"/>
+      <c r="W34" s="36"/>
+      <c r="X34" s="36"/>
+      <c r="Y34" s="36"/>
+      <c r="Z34" s="36"/>
+      <c r="AA34" s="36"/>
+      <c r="AB34" s="36"/>
+      <c r="AC34" s="36"/>
+      <c r="AD34" s="36"/>
+      <c r="AE34" s="36"/>
+      <c r="AF34" s="36"/>
+      <c r="AG34" s="36"/>
       <c r="AH34" s="1"/>
       <c r="AI34" s="1"/>
       <c r="AJ34" s="1"/>
@@ -2497,21 +2524,21 @@
       <c r="P36" s="8"/>
       <c r="Q36" s="8"/>
       <c r="R36" s="1"/>
-      <c r="S36" s="12"/>
-      <c r="T36" s="13"/>
-      <c r="U36" s="13"/>
-      <c r="V36" s="13"/>
-      <c r="W36" s="13"/>
-      <c r="X36" s="13"/>
-      <c r="Y36" s="13"/>
-      <c r="Z36" s="13"/>
-      <c r="AA36" s="13"/>
-      <c r="AB36" s="13"/>
-      <c r="AC36" s="13"/>
-      <c r="AD36" s="13"/>
-      <c r="AE36" s="13"/>
-      <c r="AF36" s="13"/>
-      <c r="AG36" s="13"/>
+      <c r="S36" s="34"/>
+      <c r="T36" s="26"/>
+      <c r="U36" s="26"/>
+      <c r="V36" s="26"/>
+      <c r="W36" s="26"/>
+      <c r="X36" s="26"/>
+      <c r="Y36" s="26"/>
+      <c r="Z36" s="26"/>
+      <c r="AA36" s="26"/>
+      <c r="AB36" s="26"/>
+      <c r="AC36" s="26"/>
+      <c r="AD36" s="26"/>
+      <c r="AE36" s="26"/>
+      <c r="AF36" s="26"/>
+      <c r="AG36" s="26"/>
       <c r="AH36" s="1"/>
       <c r="AI36" s="1"/>
       <c r="AJ36" s="1"/>
@@ -2528,34 +2555,34 @@
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
-      <c r="J37" s="14" t="s">
+      <c r="J37" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="K37" s="15"/>
-      <c r="L37" s="15"/>
-      <c r="M37" s="15"/>
-      <c r="N37" s="15"/>
-      <c r="O37" s="15"/>
-      <c r="P37" s="15"/>
-      <c r="Q37" s="15"/>
+      <c r="K37" s="36"/>
+      <c r="L37" s="36"/>
+      <c r="M37" s="36"/>
+      <c r="N37" s="36"/>
+      <c r="O37" s="36"/>
+      <c r="P37" s="36"/>
+      <c r="Q37" s="36"/>
       <c r="R37" s="9"/>
-      <c r="S37" s="14" t="s">
+      <c r="S37" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="T37" s="15"/>
-      <c r="U37" s="15"/>
-      <c r="V37" s="15"/>
-      <c r="W37" s="15"/>
-      <c r="X37" s="15"/>
-      <c r="Y37" s="15"/>
-      <c r="Z37" s="15"/>
-      <c r="AA37" s="15"/>
-      <c r="AB37" s="15"/>
-      <c r="AC37" s="15"/>
-      <c r="AD37" s="15"/>
-      <c r="AE37" s="15"/>
-      <c r="AF37" s="15"/>
-      <c r="AG37" s="15"/>
+      <c r="T37" s="36"/>
+      <c r="U37" s="36"/>
+      <c r="V37" s="36"/>
+      <c r="W37" s="36"/>
+      <c r="X37" s="36"/>
+      <c r="Y37" s="36"/>
+      <c r="Z37" s="36"/>
+      <c r="AA37" s="36"/>
+      <c r="AB37" s="36"/>
+      <c r="AC37" s="36"/>
+      <c r="AD37" s="36"/>
+      <c r="AE37" s="36"/>
+      <c r="AF37" s="36"/>
+      <c r="AG37" s="36"/>
       <c r="AH37" s="1"/>
       <c r="AI37" s="1"/>
       <c r="AJ37" s="1"/>
@@ -40966,6 +40993,45 @@
     </row>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="S33:AG33"/>
+    <mergeCell ref="J34:Q34"/>
+    <mergeCell ref="S34:AG34"/>
+    <mergeCell ref="S36:AG36"/>
+    <mergeCell ref="J37:Q37"/>
+    <mergeCell ref="S37:AG37"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="G19:AL19"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="AF21:AK21"/>
+    <mergeCell ref="D21:R21"/>
+    <mergeCell ref="S21:V21"/>
+    <mergeCell ref="B11:T11"/>
+    <mergeCell ref="B13:AL14"/>
+    <mergeCell ref="B15:AL15"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="G17:AL17"/>
+    <mergeCell ref="B2:T3"/>
+    <mergeCell ref="U2:X2"/>
+    <mergeCell ref="Y2:AL2"/>
+    <mergeCell ref="Y3:AL4"/>
+    <mergeCell ref="B4:T4"/>
+    <mergeCell ref="U3:X4"/>
+    <mergeCell ref="W23:Y23"/>
+    <mergeCell ref="D23:R23"/>
+    <mergeCell ref="S23:V23"/>
+    <mergeCell ref="U5:X5"/>
+    <mergeCell ref="U6:X7"/>
+    <mergeCell ref="U8:X11"/>
+    <mergeCell ref="Y5:AL5"/>
+    <mergeCell ref="Y6:AL7"/>
+    <mergeCell ref="Y8:AL11"/>
+    <mergeCell ref="B5:T6"/>
+    <mergeCell ref="B7:T7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:T8"/>
+    <mergeCell ref="B9:T10"/>
     <mergeCell ref="Z23:AE23"/>
     <mergeCell ref="AF23:AK23"/>
     <mergeCell ref="B28:AL28"/>
@@ -40982,45 +41048,6 @@
     <mergeCell ref="S22:V22"/>
     <mergeCell ref="W22:Y22"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="W23:Y23"/>
-    <mergeCell ref="D23:R23"/>
-    <mergeCell ref="S23:V23"/>
-    <mergeCell ref="U5:X5"/>
-    <mergeCell ref="U6:X7"/>
-    <mergeCell ref="U8:X11"/>
-    <mergeCell ref="Y5:AL5"/>
-    <mergeCell ref="Y6:AL7"/>
-    <mergeCell ref="Y8:AL11"/>
-    <mergeCell ref="B5:T6"/>
-    <mergeCell ref="B7:T7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:T8"/>
-    <mergeCell ref="B9:T10"/>
-    <mergeCell ref="B2:T3"/>
-    <mergeCell ref="U2:X2"/>
-    <mergeCell ref="Y2:AL2"/>
-    <mergeCell ref="Y3:AL4"/>
-    <mergeCell ref="B4:T4"/>
-    <mergeCell ref="U3:X4"/>
-    <mergeCell ref="B11:T11"/>
-    <mergeCell ref="B13:AL14"/>
-    <mergeCell ref="B15:AL15"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="G17:AL17"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="G19:AL19"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="AF21:AK21"/>
-    <mergeCell ref="D21:R21"/>
-    <mergeCell ref="S21:V21"/>
-    <mergeCell ref="S33:AG33"/>
-    <mergeCell ref="J34:Q34"/>
-    <mergeCell ref="S34:AG34"/>
-    <mergeCell ref="S36:AG36"/>
-    <mergeCell ref="J37:Q37"/>
-    <mergeCell ref="S37:AG37"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="97" orientation="portrait" r:id="rId1"/>
